--- a/artfynd/A 56940-2025 artfynd.xlsx
+++ b/artfynd/A 56940-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129998685</v>
       </c>
       <c r="B2" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129998684</v>
       </c>
       <c r="B3" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129998697</v>
+        <v>129998703</v>
       </c>
       <c r="B4" t="n">
-        <v>78842</v>
+        <v>8451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433506</v>
+        <v>432909</v>
       </c>
       <c r="R4" t="n">
-        <v>6765247</v>
+        <v>6765182</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129998703</v>
+        <v>129998697</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>78845</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432909</v>
+        <v>433506</v>
       </c>
       <c r="R5" t="n">
-        <v>6765182</v>
+        <v>6765247</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1066,7 +1066,7 @@
         <v>129998708</v>
       </c>
       <c r="B6" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129998686</v>
       </c>
       <c r="B7" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129998706</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129998718</v>
       </c>
       <c r="B9" t="n">
-        <v>79085</v>
+        <v>79088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>129998683</v>
       </c>
       <c r="B10" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1549,32 +1549,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129998704</v>
+        <v>129998717</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>79088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>230405</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>432886</v>
+        <v>433514</v>
       </c>
       <c r="R11" t="n">
-        <v>6765067</v>
+        <v>6765225</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1628,6 +1628,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1646,32 +1647,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129998717</v>
+        <v>129998704</v>
       </c>
       <c r="B12" t="n">
-        <v>79085</v>
+        <v>8451</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>230405</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1681,10 +1682,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433514</v>
+        <v>432886</v>
       </c>
       <c r="R12" t="n">
-        <v>6765225</v>
+        <v>6765067</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1725,7 +1726,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1747,7 +1747,7 @@
         <v>129998698</v>
       </c>
       <c r="B13" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129998687</v>
       </c>
       <c r="B14" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>129998716</v>
       </c>
       <c r="B15" t="n">
-        <v>79085</v>
+        <v>79088</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>129998688</v>
       </c>
       <c r="B16" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,32 +2133,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129998701</v>
+        <v>129998690</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>91626</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433145</v>
+        <v>433075</v>
       </c>
       <c r="R17" t="n">
-        <v>6765198</v>
+        <v>6765183</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2206,13 +2206,17 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1 st. Inte samma träd som tickorna bredvid.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2231,32 +2235,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129998719</v>
+        <v>129998701</v>
       </c>
       <c r="B18" t="n">
-        <v>79085</v>
+        <v>8451</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>230405</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2266,10 +2270,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>432725</v>
+        <v>433145</v>
       </c>
       <c r="R18" t="n">
-        <v>6764934</v>
+        <v>6765198</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2329,10 +2333,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129998690</v>
+        <v>129998719</v>
       </c>
       <c r="B19" t="n">
-        <v>91623</v>
+        <v>79088</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,21 +2344,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>230405</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433075</v>
+        <v>432725</v>
       </c>
       <c r="R19" t="n">
-        <v>6765183</v>
+        <v>6764934</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2402,17 +2406,13 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>1 st. Inte samma träd som tickorna bredvid.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2428,6 +2428,6616 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130009997</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>433474</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6765288</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130010428</v>
+      </c>
+      <c r="B21" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>432868</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6764991</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130009995</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>433498</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6765316</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130010431</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>432755</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6764944</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130000797</v>
+      </c>
+      <c r="B24" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Fisktjärnfjot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>432910</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6764964</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130000805</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Fisktjärnfjot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>432810</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6765134</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130010447</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78095</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>432743</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6764890</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130010439</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>432941</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6764955</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130010002</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>432842</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6764945</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130009984</v>
+      </c>
+      <c r="B29" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>432757</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6764953</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130009976</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79677</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>432806</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6764957</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130000803</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Fisktjärnfjot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>433436</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6765320</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130009999</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>433404</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6765152</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>130010440</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>432846</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6764945</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>130010446</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78095</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>432787</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6764952</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>130000795</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79677</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Fisktjärnfjot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>432795</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6764980</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>130009975</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79677</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>432801</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6765083</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>130009986</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>432880</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6764902</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>130009980</v>
+      </c>
+      <c r="B38" t="n">
+        <v>90637</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>433320</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6765160</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>130009982</v>
+      </c>
+      <c r="B39" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>433497</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6765321</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>130010425</v>
+      </c>
+      <c r="B40" t="n">
+        <v>90637</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>432853</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6765042</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>130009998</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>433400</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6765137</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>130010442</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>432625</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6764870</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>130010444</v>
+      </c>
+      <c r="B43" t="n">
+        <v>92887</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>433284</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6765098</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>130010424</v>
+      </c>
+      <c r="B44" t="n">
+        <v>90637</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>433000</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6765168</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>130010429</v>
+      </c>
+      <c r="B45" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>432898</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6764968</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>130009993</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>433494</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6765320</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>130000806</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Fisktjärnfjot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>432829</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6765145</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>130000800</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79088</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Fisktjärnfjot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>433464</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6765289</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>130009994</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>433500</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6765331</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>130010441</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>432847</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6764943</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>130000808</v>
+      </c>
+      <c r="B51" t="n">
+        <v>92887</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Fisktjärnfjot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>432783</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6765102</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>130010438</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>432834</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6765072</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>130009978</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91626</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>433075</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6765186</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>130009983</v>
+      </c>
+      <c r="B54" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>432870</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6764928</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>130010437</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>433359</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6765114</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>130010427</v>
+      </c>
+      <c r="B56" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>433049</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6765172</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>130010423</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79677</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>432753</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6765037</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>130000802</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Fisktjärnfjot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>432785</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6765104</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>130010436</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>433362</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6765100</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>130009989</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>433473</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6765313</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>130009981</v>
+      </c>
+      <c r="B61" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>433429</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6765324</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>130009991</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>433469</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6765340</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>130010000</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>432861</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6764984</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>130010434</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>433459</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6765287</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>130009979</v>
+      </c>
+      <c r="B65" t="n">
+        <v>91626</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>433285</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6765090</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>130010426</v>
+      </c>
+      <c r="B66" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>433443</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6765297</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>130010004</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>432836</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6764947</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>130009992</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>433482</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6765315</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>130009996</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>433488</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6765315</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>130010432</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>432782</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6765113</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>130010001</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>432965</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6764935</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>130010433</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>432809</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6765129</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>130010005</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>432732</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6764932</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>130000796</v>
+      </c>
+      <c r="B74" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Fisktjärnfjot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>433217</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6765206</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>130009990</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>433472</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6765327</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>130010435</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>433498</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6765212</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>130009988</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>433439</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6765313</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>130000798</v>
+      </c>
+      <c r="B78" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Fisktjärnfjot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>432873</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6764999</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>130010003</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>432841</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6764949</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>130010445</v>
+      </c>
+      <c r="B80" t="n">
+        <v>78095</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>433119</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6765204</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>130010430</v>
+      </c>
+      <c r="B81" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>432802</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6764963</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>130009987</v>
+      </c>
+      <c r="B82" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>433174</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6765214</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56940-2025 artfynd.xlsx
+++ b/artfynd/A 56940-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY82"/>
+  <dimension ref="A1:AY83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1452,32 +1452,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129998683</v>
+        <v>129998704</v>
       </c>
       <c r="B10" t="n">
-        <v>79677</v>
+        <v>8451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433347</v>
+        <v>432886</v>
       </c>
       <c r="R10" t="n">
-        <v>6765088</v>
+        <v>6765067</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1549,10 +1549,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129998717</v>
+        <v>129998683</v>
       </c>
       <c r="B11" t="n">
-        <v>79088</v>
+        <v>79677</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1560,21 +1560,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>230405</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433514</v>
+        <v>433347</v>
       </c>
       <c r="R11" t="n">
-        <v>6765225</v>
+        <v>6765088</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1628,7 +1628,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1647,32 +1646,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129998704</v>
+        <v>129998717</v>
       </c>
       <c r="B12" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>230405</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1682,10 +1681,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432886</v>
+        <v>433514</v>
       </c>
       <c r="R12" t="n">
-        <v>6765067</v>
+        <v>6765225</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1726,6 +1725,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -3996,7 +3996,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130000795</v>
+        <v>130009975</v>
       </c>
       <c r="B35" t="n">
         <v>79677</v>
@@ -4027,14 +4027,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>432795</v>
+        <v>432801</v>
       </c>
       <c r="R35" t="n">
-        <v>6764980</v>
+        <v>6765083</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4091,22 +4091,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130009975</v>
+        <v>130009986</v>
       </c>
       <c r="B36" t="n">
-        <v>79677</v>
+        <v>78844</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4114,21 +4114,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4138,10 +4138,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>432801</v>
+        <v>432880</v>
       </c>
       <c r="R36" t="n">
-        <v>6765083</v>
+        <v>6764902</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4210,10 +4210,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130009986</v>
+        <v>130000795</v>
       </c>
       <c r="B37" t="n">
-        <v>78844</v>
+        <v>79677</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4221,34 +4221,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>432880</v>
+        <v>432795</v>
       </c>
       <c r="R37" t="n">
-        <v>6764902</v>
+        <v>6764980</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4305,12 +4305,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -9039,6 +9039,104 @@
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>129998689</v>
+      </c>
+      <c r="B83" t="n">
+        <v>91878</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>65</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Fläckporing</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Anthoporia albobrunnea</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljoten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>433431</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6765309</v>
+      </c>
+      <c r="S83" t="n">
+        <v>1</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56940-2025 artfynd.xlsx
+++ b/artfynd/A 56940-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129998703</v>
+        <v>129998697</v>
       </c>
       <c r="B4" t="n">
-        <v>8451</v>
+        <v>78845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432909</v>
+        <v>433506</v>
       </c>
       <c r="R4" t="n">
-        <v>6765182</v>
+        <v>6765247</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129998697</v>
+        <v>129998703</v>
       </c>
       <c r="B5" t="n">
-        <v>78845</v>
+        <v>8451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>433506</v>
+        <v>432909</v>
       </c>
       <c r="R5" t="n">
-        <v>6765247</v>
+        <v>6765182</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -2849,45 +2849,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130000797</v>
+        <v>130010447</v>
       </c>
       <c r="B24" t="n">
-        <v>8451</v>
+        <v>78095</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6487</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>432910</v>
+        <v>432743</v>
       </c>
       <c r="R24" t="n">
-        <v>6764964</v>
+        <v>6764890</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2917,19 +2917,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2944,44 +2934,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130000805</v>
+        <v>130000797</v>
       </c>
       <c r="B25" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2991,10 +2981,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>432810</v>
+        <v>432910</v>
       </c>
       <c r="R25" t="n">
-        <v>6765134</v>
+        <v>6764964</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3026,7 +3016,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3036,7 +3026,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3063,10 +3053,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130010447</v>
+        <v>130000805</v>
       </c>
       <c r="B26" t="n">
-        <v>78095</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3074,34 +3064,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>432743</v>
+        <v>432810</v>
       </c>
       <c r="R26" t="n">
-        <v>6764890</v>
+        <v>6765134</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3131,9 +3121,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3148,12 +3148,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 56940-2025 artfynd.xlsx
+++ b/artfynd/A 56940-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129998685</v>
       </c>
       <c r="B2" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129998684</v>
       </c>
       <c r="B3" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129998697</v>
       </c>
       <c r="B4" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129998708</v>
       </c>
       <c r="B6" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129998686</v>
       </c>
       <c r="B7" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129998718</v>
       </c>
       <c r="B9" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>129998683</v>
       </c>
       <c r="B11" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>129998717</v>
       </c>
       <c r="B12" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>129998698</v>
       </c>
       <c r="B13" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129998687</v>
       </c>
       <c r="B14" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>129998716</v>
       </c>
       <c r="B15" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>129998688</v>
       </c>
       <c r="B16" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>129998690</v>
       </c>
       <c r="B17" t="n">
-        <v>91626</v>
+        <v>91627</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2235,32 +2235,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129998701</v>
+        <v>129998719</v>
       </c>
       <c r="B18" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>230405</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433145</v>
+        <v>432725</v>
       </c>
       <c r="R18" t="n">
-        <v>6765198</v>
+        <v>6764934</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2333,32 +2333,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129998719</v>
+        <v>129998701</v>
       </c>
       <c r="B19" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>230405</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432725</v>
+        <v>433145</v>
       </c>
       <c r="R19" t="n">
-        <v>6764934</v>
+        <v>6765198</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2434,7 +2434,7 @@
         <v>130009997</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2538,54 +2538,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130010428</v>
+        <v>130009995</v>
       </c>
       <c r="B21" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>432868</v>
+        <v>433498</v>
       </c>
       <c r="R21" t="n">
-        <v>6764991</v>
+        <v>6765316</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2615,40 +2606,49 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130009995</v>
+        <v>130010431</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2656,21 +2656,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>433498</v>
+        <v>432755</v>
       </c>
       <c r="R22" t="n">
-        <v>6765316</v>
+        <v>6764944</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2713,19 +2713,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2740,57 +2730,66 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130010431</v>
+        <v>130010428</v>
       </c>
       <c r="B23" t="n">
-        <v>78844</v>
+        <v>8451</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>432755</v>
+        <v>432868</v>
       </c>
       <c r="R23" t="n">
-        <v>6764944</v>
+        <v>6764991</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2831,6 +2830,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2849,10 +2849,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130010447</v>
+        <v>130000805</v>
       </c>
       <c r="B24" t="n">
-        <v>78095</v>
+        <v>79088</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2860,34 +2860,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>432743</v>
+        <v>432810</v>
       </c>
       <c r="R24" t="n">
-        <v>6764890</v>
+        <v>6765134</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2917,9 +2917,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2934,57 +2944,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130000797</v>
+        <v>130010447</v>
       </c>
       <c r="B25" t="n">
-        <v>8451</v>
+        <v>78095</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6487</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>432910</v>
+        <v>432743</v>
       </c>
       <c r="R25" t="n">
-        <v>6764964</v>
+        <v>6764890</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3014,19 +3024,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3041,44 +3041,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130000805</v>
+        <v>130000797</v>
       </c>
       <c r="B26" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>432810</v>
+        <v>432910</v>
       </c>
       <c r="R26" t="n">
-        <v>6765134</v>
+        <v>6764964</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3160,45 +3160,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130010439</v>
+        <v>130009984</v>
       </c>
       <c r="B27" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>432941</v>
+        <v>432757</v>
       </c>
       <c r="R27" t="n">
-        <v>6764955</v>
+        <v>6764953</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3228,39 +3237,50 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130010002</v>
+        <v>130009976</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>79678</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3268,21 +3288,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3292,10 +3312,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>432842</v>
+        <v>432806</v>
       </c>
       <c r="R28" t="n">
-        <v>6764945</v>
+        <v>6764957</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3327,7 +3347,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3337,7 +3357,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3364,54 +3384,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130009984</v>
+        <v>130010439</v>
       </c>
       <c r="B29" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>432757</v>
+        <v>432941</v>
       </c>
       <c r="R29" t="n">
-        <v>6764953</v>
+        <v>6764955</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3441,50 +3452,39 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130009976</v>
+        <v>130010002</v>
       </c>
       <c r="B30" t="n">
-        <v>79677</v>
+        <v>79088</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3492,21 +3492,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>432806</v>
+        <v>432842</v>
       </c>
       <c r="R30" t="n">
-        <v>6764957</v>
+        <v>6764945</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3591,7 +3591,7 @@
         <v>130000803</v>
       </c>
       <c r="B31" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>130009999</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>130010440</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>130009975</v>
       </c>
       <c r="B35" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4103,10 +4103,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130009986</v>
+        <v>130000795</v>
       </c>
       <c r="B36" t="n">
-        <v>78844</v>
+        <v>79678</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4114,34 +4114,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>432880</v>
+        <v>432795</v>
       </c>
       <c r="R36" t="n">
-        <v>6764902</v>
+        <v>6764980</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4198,22 +4198,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130000795</v>
+        <v>130009986</v>
       </c>
       <c r="B37" t="n">
-        <v>79677</v>
+        <v>78845</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4221,34 +4221,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>432795</v>
+        <v>432880</v>
       </c>
       <c r="R37" t="n">
-        <v>6764980</v>
+        <v>6764902</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4305,12 +4305,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4320,7 +4320,7 @@
         <v>130009980</v>
       </c>
       <c r="B38" t="n">
-        <v>90637</v>
+        <v>90638</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4425,54 +4425,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130009982</v>
+        <v>130010425</v>
       </c>
       <c r="B39" t="n">
-        <v>8451</v>
+        <v>90638</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>1962</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>433497</v>
+        <v>432853</v>
       </c>
       <c r="R39" t="n">
-        <v>6765321</v>
+        <v>6765042</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4502,85 +4493,83 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130010425</v>
+        <v>130009982</v>
       </c>
       <c r="B40" t="n">
-        <v>90637</v>
+        <v>8451</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>432853</v>
+        <v>433497</v>
       </c>
       <c r="R40" t="n">
-        <v>6765042</v>
+        <v>6765321</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4610,39 +4599,50 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130009998</v>
+        <v>130010442</v>
       </c>
       <c r="B41" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4674,10 +4674,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>433400</v>
+        <v>432625</v>
       </c>
       <c r="R41" t="n">
-        <v>6765137</v>
+        <v>6764870</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4707,19 +4707,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4734,22 +4724,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130010442</v>
+        <v>130009998</v>
       </c>
       <c r="B42" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4781,10 +4771,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>432625</v>
+        <v>433400</v>
       </c>
       <c r="R42" t="n">
-        <v>6764870</v>
+        <v>6765137</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4814,9 +4804,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4831,12 +4831,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4846,7 +4846,7 @@
         <v>130010444</v>
       </c>
       <c r="B43" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4940,45 +4940,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130010424</v>
+        <v>130010429</v>
       </c>
       <c r="B44" t="n">
-        <v>90637</v>
+        <v>8451</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>433000</v>
+        <v>432898</v>
       </c>
       <c r="R44" t="n">
-        <v>6765168</v>
+        <v>6764968</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5019,6 +5028,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5037,54 +5047,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130010429</v>
+        <v>130000800</v>
       </c>
       <c r="B45" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>230405</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>432898</v>
+        <v>433464</v>
       </c>
       <c r="R45" t="n">
-        <v>6764968</v>
+        <v>6765289</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5114,9 +5115,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5132,22 +5143,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130009993</v>
+        <v>130010424</v>
       </c>
       <c r="B46" t="n">
-        <v>79087</v>
+        <v>90638</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5155,21 +5166,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5179,10 +5190,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>433494</v>
+        <v>433000</v>
       </c>
       <c r="R46" t="n">
-        <v>6765320</v>
+        <v>6765168</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5212,19 +5223,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:58</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5239,12 +5240,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5254,7 +5255,7 @@
         <v>130000806</v>
       </c>
       <c r="B47" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5358,7 +5359,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130000800</v>
+        <v>130009993</v>
       </c>
       <c r="B48" t="n">
         <v>79088</v>
@@ -5369,16 +5370,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5389,14 +5390,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>433464</v>
+        <v>433494</v>
       </c>
       <c r="R48" t="n">
-        <v>6765289</v>
+        <v>6765320</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5428,7 +5429,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5438,7 +5439,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5447,19 +5448,18 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5469,7 +5469,7 @@
         <v>130009994</v>
       </c>
       <c r="B49" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>130010441</v>
       </c>
       <c r="B50" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>130000808</v>
       </c>
       <c r="B51" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>130010438</v>
       </c>
       <c r="B52" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>130009978</v>
       </c>
       <c r="B53" t="n">
-        <v>91626</v>
+        <v>91627</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6115,32 +6115,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130010437</v>
+        <v>130010427</v>
       </c>
       <c r="B55" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6150,10 +6150,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>433359</v>
+        <v>433049</v>
       </c>
       <c r="R55" t="n">
-        <v>6765114</v>
+        <v>6765172</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6212,32 +6212,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130010427</v>
+        <v>130010423</v>
       </c>
       <c r="B56" t="n">
-        <v>8451</v>
+        <v>79678</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>433049</v>
+        <v>432753</v>
       </c>
       <c r="R56" t="n">
-        <v>6765172</v>
+        <v>6765037</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6309,10 +6309,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130010423</v>
+        <v>130010437</v>
       </c>
       <c r="B57" t="n">
-        <v>79677</v>
+        <v>79088</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6320,21 +6320,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>432753</v>
+        <v>433359</v>
       </c>
       <c r="R57" t="n">
-        <v>6765037</v>
+        <v>6765114</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6409,7 +6409,7 @@
         <v>130000802</v>
       </c>
       <c r="B58" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>130010436</v>
       </c>
       <c r="B59" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>130009989</v>
       </c>
       <c r="B60" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6717,54 +6717,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130009981</v>
+        <v>130009991</v>
       </c>
       <c r="B61" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>433429</v>
+        <v>433469</v>
       </c>
       <c r="R61" t="n">
-        <v>6765324</v>
+        <v>6765340</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6796,7 +6787,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6806,7 +6797,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6815,7 +6806,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6834,10 +6824,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130009991</v>
+        <v>130010000</v>
       </c>
       <c r="B62" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6869,10 +6859,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>433469</v>
+        <v>432861</v>
       </c>
       <c r="R62" t="n">
-        <v>6765340</v>
+        <v>6764984</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6904,7 +6894,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -6914,7 +6904,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6941,45 +6931,54 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130010000</v>
+        <v>130009981</v>
       </c>
       <c r="B63" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>432861</v>
+        <v>433429</v>
       </c>
       <c r="R63" t="n">
-        <v>6764984</v>
+        <v>6765324</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7011,7 +7010,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7021,7 +7020,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7030,6 +7029,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7048,45 +7048,54 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130010434</v>
+        <v>130010426</v>
       </c>
       <c r="B64" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>433459</v>
+        <v>433443</v>
       </c>
       <c r="R64" t="n">
-        <v>6765287</v>
+        <v>6765297</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7127,6 +7136,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7145,10 +7155,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130009979</v>
+        <v>130010434</v>
       </c>
       <c r="B65" t="n">
-        <v>91626</v>
+        <v>79088</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7156,21 +7166,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7180,10 +7190,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>433285</v>
+        <v>433459</v>
       </c>
       <c r="R65" t="n">
-        <v>6765090</v>
+        <v>6765287</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7213,19 +7223,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7240,66 +7240,57 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130010426</v>
+        <v>130010004</v>
       </c>
       <c r="B66" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>433443</v>
+        <v>432836</v>
       </c>
       <c r="R66" t="n">
-        <v>6765297</v>
+        <v>6764947</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7329,40 +7320,49 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130010004</v>
+        <v>130009979</v>
       </c>
       <c r="B67" t="n">
-        <v>79087</v>
+        <v>91627</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7370,21 +7370,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7394,10 +7394,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>432836</v>
+        <v>433285</v>
       </c>
       <c r="R67" t="n">
-        <v>6764947</v>
+        <v>6765090</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7469,7 +7469,7 @@
         <v>130009992</v>
       </c>
       <c r="B68" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>130009996</v>
       </c>
       <c r="B69" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>130010432</v>
       </c>
       <c r="B70" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>130010001</v>
       </c>
       <c r="B71" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7884,45 +7884,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130010433</v>
+        <v>130000796</v>
       </c>
       <c r="B72" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>432809</v>
+        <v>433217</v>
       </c>
       <c r="R72" t="n">
-        <v>6765129</v>
+        <v>6765206</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7952,9 +7952,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7969,22 +7979,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130010005</v>
+        <v>130010433</v>
       </c>
       <c r="B73" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8016,10 +8026,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432732</v>
+        <v>432809</v>
       </c>
       <c r="R73" t="n">
-        <v>6764932</v>
+        <v>6765129</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8049,19 +8059,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>10:35</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8076,57 +8076,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130000796</v>
+        <v>130010005</v>
       </c>
       <c r="B74" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>433217</v>
+        <v>432732</v>
       </c>
       <c r="R74" t="n">
-        <v>6765206</v>
+        <v>6764932</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8168,7 +8168,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8183,12 +8183,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8198,7 +8198,7 @@
         <v>130009990</v>
       </c>
       <c r="B75" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>130010435</v>
       </c>
       <c r="B76" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>130009988</v>
       </c>
       <c r="B77" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>130010003</v>
       </c>
       <c r="B79" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>129998689</v>
       </c>
       <c r="B83" t="n">
-        <v>91878</v>
+        <v>91879</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 56940-2025 artfynd.xlsx
+++ b/artfynd/A 56940-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129998697</v>
+        <v>129998703</v>
       </c>
       <c r="B4" t="n">
-        <v>78846</v>
+        <v>8451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433506</v>
+        <v>432909</v>
       </c>
       <c r="R4" t="n">
-        <v>6765247</v>
+        <v>6765182</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129998703</v>
+        <v>129998697</v>
       </c>
       <c r="B5" t="n">
-        <v>8451</v>
+        <v>78846</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432909</v>
+        <v>433506</v>
       </c>
       <c r="R5" t="n">
-        <v>6765182</v>
+        <v>6765247</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -4639,7 +4639,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130010442</v>
+        <v>130009998</v>
       </c>
       <c r="B41" t="n">
         <v>79088</v>
@@ -4674,10 +4674,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>432625</v>
+        <v>433400</v>
       </c>
       <c r="R41" t="n">
-        <v>6764870</v>
+        <v>6765137</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4707,9 +4707,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4724,19 +4734,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130009998</v>
+        <v>130010442</v>
       </c>
       <c r="B42" t="n">
         <v>79088</v>
@@ -4771,10 +4781,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>433400</v>
+        <v>432625</v>
       </c>
       <c r="R42" t="n">
-        <v>6765137</v>
+        <v>6764870</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4804,19 +4814,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4831,22 +4831,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130010444</v>
+        <v>130010429</v>
       </c>
       <c r="B43" t="n">
-        <v>92888</v>
+        <v>8451</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4854,34 +4854,43 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>433284</v>
+        <v>432898</v>
       </c>
       <c r="R43" t="n">
-        <v>6765098</v>
+        <v>6764968</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4922,6 +4931,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4940,54 +4950,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130010429</v>
+        <v>130010424</v>
       </c>
       <c r="B44" t="n">
-        <v>8451</v>
+        <v>90638</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>1962</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>432898</v>
+        <v>433000</v>
       </c>
       <c r="R44" t="n">
-        <v>6764968</v>
+        <v>6765168</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5028,7 +5029,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5047,10 +5047,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130000800</v>
+        <v>130000806</v>
       </c>
       <c r="B45" t="n">
-        <v>79089</v>
+        <v>79088</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5058,16 +5058,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>433464</v>
+        <v>432829</v>
       </c>
       <c r="R45" t="n">
-        <v>6765289</v>
+        <v>6765145</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5136,7 +5136,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5155,10 +5154,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130010424</v>
+        <v>130009993</v>
       </c>
       <c r="B46" t="n">
-        <v>90638</v>
+        <v>79088</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5166,21 +5165,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5190,10 +5189,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>433000</v>
+        <v>433494</v>
       </c>
       <c r="R46" t="n">
-        <v>6765168</v>
+        <v>6765320</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5223,9 +5222,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5240,57 +5249,57 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130000806</v>
+        <v>130010444</v>
       </c>
       <c r="B47" t="n">
-        <v>79088</v>
+        <v>92888</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>432829</v>
+        <v>433284</v>
       </c>
       <c r="R47" t="n">
-        <v>6765145</v>
+        <v>6765098</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5320,19 +5329,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5347,22 +5346,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130009993</v>
+        <v>130000800</v>
       </c>
       <c r="B48" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5370,16 +5369,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5390,14 +5389,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>433494</v>
+        <v>433464</v>
       </c>
       <c r="R48" t="n">
-        <v>6765320</v>
+        <v>6765289</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5429,7 +5428,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5439,7 +5438,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5448,18 +5447,19 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6115,32 +6115,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130010427</v>
+        <v>130010437</v>
       </c>
       <c r="B55" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6150,10 +6150,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>433049</v>
+        <v>433359</v>
       </c>
       <c r="R55" t="n">
-        <v>6765172</v>
+        <v>6765114</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6212,10 +6212,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130010423</v>
+        <v>130000802</v>
       </c>
       <c r="B56" t="n">
-        <v>79678</v>
+        <v>79088</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6223,34 +6223,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>432753</v>
+        <v>432785</v>
       </c>
       <c r="R56" t="n">
-        <v>6765037</v>
+        <v>6765104</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6280,9 +6280,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6297,44 +6307,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130010437</v>
+        <v>130010427</v>
       </c>
       <c r="B57" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6344,10 +6354,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>433359</v>
+        <v>433049</v>
       </c>
       <c r="R57" t="n">
-        <v>6765114</v>
+        <v>6765172</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6406,10 +6416,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130000802</v>
+        <v>130010423</v>
       </c>
       <c r="B58" t="n">
-        <v>79088</v>
+        <v>79678</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6417,34 +6427,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>432785</v>
+        <v>432753</v>
       </c>
       <c r="R58" t="n">
-        <v>6765104</v>
+        <v>6765037</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6474,19 +6484,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>14:54</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6501,12 +6501,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7048,54 +7048,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130010426</v>
+        <v>130010434</v>
       </c>
       <c r="B64" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>433443</v>
+        <v>433459</v>
       </c>
       <c r="R64" t="n">
-        <v>6765297</v>
+        <v>6765287</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7136,7 +7127,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7155,7 +7145,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130010434</v>
+        <v>130010004</v>
       </c>
       <c r="B65" t="n">
         <v>79088</v>
@@ -7190,10 +7180,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>433459</v>
+        <v>432836</v>
       </c>
       <c r="R65" t="n">
-        <v>6765287</v>
+        <v>6764947</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7223,9 +7213,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7240,57 +7240,66 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130010004</v>
+        <v>130010426</v>
       </c>
       <c r="B66" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>432836</v>
+        <v>433443</v>
       </c>
       <c r="R66" t="n">
-        <v>6764947</v>
+        <v>6765297</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7320,39 +7329,30 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>

--- a/artfynd/A 56940-2025 artfynd.xlsx
+++ b/artfynd/A 56940-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129998703</v>
+        <v>129998697</v>
       </c>
       <c r="B4" t="n">
-        <v>8451</v>
+        <v>78846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432909</v>
+        <v>433506</v>
       </c>
       <c r="R4" t="n">
-        <v>6765182</v>
+        <v>6765247</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129998697</v>
+        <v>129998703</v>
       </c>
       <c r="B5" t="n">
-        <v>78846</v>
+        <v>8451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>433506</v>
+        <v>432909</v>
       </c>
       <c r="R5" t="n">
-        <v>6765247</v>
+        <v>6765182</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -3996,10 +3996,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130009975</v>
+        <v>130009986</v>
       </c>
       <c r="B35" t="n">
-        <v>79678</v>
+        <v>78845</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4007,21 +4007,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4031,10 +4031,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>432801</v>
+        <v>432880</v>
       </c>
       <c r="R35" t="n">
-        <v>6765083</v>
+        <v>6764902</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4103,7 +4103,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130000795</v>
+        <v>130009975</v>
       </c>
       <c r="B36" t="n">
         <v>79678</v>
@@ -4134,14 +4134,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>432795</v>
+        <v>432801</v>
       </c>
       <c r="R36" t="n">
-        <v>6764980</v>
+        <v>6765083</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4198,22 +4198,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130009986</v>
+        <v>130000795</v>
       </c>
       <c r="B37" t="n">
-        <v>78845</v>
+        <v>79678</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4221,34 +4221,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>432880</v>
+        <v>432795</v>
       </c>
       <c r="R37" t="n">
-        <v>6764902</v>
+        <v>6764980</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4305,12 +4305,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4843,10 +4843,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130010429</v>
+        <v>130010444</v>
       </c>
       <c r="B43" t="n">
-        <v>8451</v>
+        <v>92888</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4854,43 +4854,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>432898</v>
+        <v>433284</v>
       </c>
       <c r="R43" t="n">
-        <v>6764968</v>
+        <v>6765098</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4931,7 +4922,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4950,45 +4940,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130010424</v>
+        <v>130010429</v>
       </c>
       <c r="B44" t="n">
-        <v>90638</v>
+        <v>8451</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>433000</v>
+        <v>432898</v>
       </c>
       <c r="R44" t="n">
-        <v>6765168</v>
+        <v>6764968</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5029,6 +5028,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5047,10 +5047,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130000806</v>
+        <v>130000800</v>
       </c>
       <c r="B45" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5058,16 +5058,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>432829</v>
+        <v>433464</v>
       </c>
       <c r="R45" t="n">
-        <v>6765145</v>
+        <v>6765289</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5136,6 +5136,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5154,10 +5155,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130009993</v>
+        <v>130010424</v>
       </c>
       <c r="B46" t="n">
-        <v>79088</v>
+        <v>90638</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5165,21 +5166,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5189,10 +5190,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>433494</v>
+        <v>433000</v>
       </c>
       <c r="R46" t="n">
-        <v>6765320</v>
+        <v>6765168</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5222,19 +5223,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:58</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5249,57 +5240,57 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130010444</v>
+        <v>130000806</v>
       </c>
       <c r="B47" t="n">
-        <v>92888</v>
+        <v>79088</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>433284</v>
+        <v>432829</v>
       </c>
       <c r="R47" t="n">
-        <v>6765098</v>
+        <v>6765145</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5329,9 +5320,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5346,22 +5347,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130000800</v>
+        <v>130009993</v>
       </c>
       <c r="B48" t="n">
-        <v>79089</v>
+        <v>79088</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5369,16 +5370,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5389,14 +5390,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>433464</v>
+        <v>433494</v>
       </c>
       <c r="R48" t="n">
-        <v>6765289</v>
+        <v>6765320</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5428,7 +5429,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5438,7 +5439,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5447,19 +5448,18 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6115,32 +6115,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130010437</v>
+        <v>130010427</v>
       </c>
       <c r="B55" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6150,10 +6150,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>433359</v>
+        <v>433049</v>
       </c>
       <c r="R55" t="n">
-        <v>6765114</v>
+        <v>6765172</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6212,10 +6212,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130000802</v>
+        <v>130010423</v>
       </c>
       <c r="B56" t="n">
-        <v>79088</v>
+        <v>79678</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6223,34 +6223,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>432785</v>
+        <v>432753</v>
       </c>
       <c r="R56" t="n">
-        <v>6765104</v>
+        <v>6765037</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6280,19 +6280,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>14:54</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6307,44 +6297,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130010427</v>
+        <v>130010437</v>
       </c>
       <c r="B57" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6354,10 +6344,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>433049</v>
+        <v>433359</v>
       </c>
       <c r="R57" t="n">
-        <v>6765172</v>
+        <v>6765114</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6416,10 +6406,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130010423</v>
+        <v>130000802</v>
       </c>
       <c r="B58" t="n">
-        <v>79678</v>
+        <v>79088</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6427,34 +6417,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>432753</v>
+        <v>432785</v>
       </c>
       <c r="R58" t="n">
-        <v>6765037</v>
+        <v>6765104</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6484,9 +6474,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6501,19 +6501,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130010436</v>
+        <v>130009991</v>
       </c>
       <c r="B59" t="n">
         <v>79088</v>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>433362</v>
+        <v>433469</v>
       </c>
       <c r="R59" t="n">
-        <v>6765100</v>
+        <v>6765340</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6581,9 +6581,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6598,19 +6608,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130009989</v>
+        <v>130010000</v>
       </c>
       <c r="B60" t="n">
         <v>79088</v>
@@ -6645,10 +6655,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>433473</v>
+        <v>432861</v>
       </c>
       <c r="R60" t="n">
-        <v>6765313</v>
+        <v>6764984</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6680,7 +6690,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6690,7 +6700,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6717,7 +6727,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130009991</v>
+        <v>130010436</v>
       </c>
       <c r="B61" t="n">
         <v>79088</v>
@@ -6752,10 +6762,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>433469</v>
+        <v>433362</v>
       </c>
       <c r="R61" t="n">
-        <v>6765340</v>
+        <v>6765100</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6785,19 +6795,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>13:59</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6812,19 +6812,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130010000</v>
+        <v>130009989</v>
       </c>
       <c r="B62" t="n">
         <v>79088</v>
@@ -6859,10 +6859,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>432861</v>
+        <v>433473</v>
       </c>
       <c r="R62" t="n">
-        <v>6764984</v>
+        <v>6765313</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7048,45 +7048,54 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130010434</v>
+        <v>130010426</v>
       </c>
       <c r="B64" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>433459</v>
+        <v>433443</v>
       </c>
       <c r="R64" t="n">
-        <v>6765287</v>
+        <v>6765297</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7127,6 +7136,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7145,7 +7155,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130010004</v>
+        <v>130010434</v>
       </c>
       <c r="B65" t="n">
         <v>79088</v>
@@ -7180,10 +7190,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432836</v>
+        <v>433459</v>
       </c>
       <c r="R65" t="n">
-        <v>6764947</v>
+        <v>6765287</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7213,19 +7223,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>10:53</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7240,66 +7240,57 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130010426</v>
+        <v>130010004</v>
       </c>
       <c r="B66" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>433443</v>
+        <v>432836</v>
       </c>
       <c r="R66" t="n">
-        <v>6765297</v>
+        <v>6764947</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7329,30 +7320,39 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>

--- a/artfynd/A 56940-2025 artfynd.xlsx
+++ b/artfynd/A 56940-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129998685</v>
       </c>
       <c r="B2" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129998684</v>
       </c>
       <c r="B3" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129998697</v>
+        <v>129998703</v>
       </c>
       <c r="B4" t="n">
-        <v>78846</v>
+        <v>8451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433506</v>
+        <v>432909</v>
       </c>
       <c r="R4" t="n">
-        <v>6765247</v>
+        <v>6765182</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129998703</v>
+        <v>129998697</v>
       </c>
       <c r="B5" t="n">
-        <v>8451</v>
+        <v>78847</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432909</v>
+        <v>433506</v>
       </c>
       <c r="R5" t="n">
-        <v>6765182</v>
+        <v>6765247</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1066,7 +1066,7 @@
         <v>129998708</v>
       </c>
       <c r="B6" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129998686</v>
       </c>
       <c r="B7" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129998718</v>
       </c>
       <c r="B9" t="n">
-        <v>79089</v>
+        <v>79090</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1452,32 +1452,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129998704</v>
+        <v>129998683</v>
       </c>
       <c r="B10" t="n">
-        <v>8451</v>
+        <v>79679</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>432886</v>
+        <v>433347</v>
       </c>
       <c r="R10" t="n">
-        <v>6765067</v>
+        <v>6765088</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1549,10 +1549,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129998683</v>
+        <v>129998717</v>
       </c>
       <c r="B11" t="n">
-        <v>79678</v>
+        <v>79090</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1560,21 +1560,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>230405</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433347</v>
+        <v>433514</v>
       </c>
       <c r="R11" t="n">
-        <v>6765088</v>
+        <v>6765225</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1628,6 +1628,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1646,32 +1647,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129998717</v>
+        <v>129998704</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>8451</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>230405</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1681,10 +1682,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433514</v>
+        <v>432886</v>
       </c>
       <c r="R12" t="n">
-        <v>6765225</v>
+        <v>6765067</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1725,7 +1726,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1747,7 +1747,7 @@
         <v>129998698</v>
       </c>
       <c r="B13" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129998687</v>
       </c>
       <c r="B14" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>129998716</v>
       </c>
       <c r="B15" t="n">
-        <v>79089</v>
+        <v>79090</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>129998688</v>
       </c>
       <c r="B16" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,32 +2133,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129998690</v>
+        <v>129998701</v>
       </c>
       <c r="B17" t="n">
-        <v>91627</v>
+        <v>8451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433075</v>
+        <v>433145</v>
       </c>
       <c r="R17" t="n">
-        <v>6765183</v>
+        <v>6765198</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2206,17 +2206,13 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>1 st. Inte samma träd som tickorna bredvid.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2235,10 +2231,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129998719</v>
+        <v>129998690</v>
       </c>
       <c r="B18" t="n">
-        <v>79089</v>
+        <v>91644</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2246,21 +2242,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>230405</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2270,10 +2266,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>432725</v>
+        <v>433075</v>
       </c>
       <c r="R18" t="n">
-        <v>6764934</v>
+        <v>6765183</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2308,13 +2304,17 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1 st. Inte samma träd som tickorna bredvid.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2333,32 +2333,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129998701</v>
+        <v>129998719</v>
       </c>
       <c r="B19" t="n">
-        <v>8451</v>
+        <v>79090</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>230405</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433145</v>
+        <v>432725</v>
       </c>
       <c r="R19" t="n">
-        <v>6765198</v>
+        <v>6764934</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130009997</v>
+        <v>130010431</v>
       </c>
       <c r="B20" t="n">
-        <v>79088</v>
+        <v>78846</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2442,21 +2442,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433474</v>
+        <v>432755</v>
       </c>
       <c r="R20" t="n">
-        <v>6765288</v>
+        <v>6764944</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2499,19 +2499,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2526,22 +2516,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130009995</v>
+        <v>130009997</v>
       </c>
       <c r="B21" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2573,10 +2563,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433498</v>
+        <v>433474</v>
       </c>
       <c r="R21" t="n">
-        <v>6765316</v>
+        <v>6765288</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2608,7 +2598,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2618,7 +2608,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2645,10 +2635,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130010431</v>
+        <v>130009995</v>
       </c>
       <c r="B22" t="n">
-        <v>78845</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2656,21 +2646,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2680,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>432755</v>
+        <v>433498</v>
       </c>
       <c r="R22" t="n">
-        <v>6764944</v>
+        <v>6765316</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2713,9 +2703,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2730,12 +2730,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2852,7 +2852,7 @@
         <v>130000805</v>
       </c>
       <c r="B24" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2956,45 +2956,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130010447</v>
+        <v>130000797</v>
       </c>
       <c r="B25" t="n">
-        <v>78095</v>
+        <v>8451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6487</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>432743</v>
+        <v>432910</v>
       </c>
       <c r="R25" t="n">
-        <v>6764890</v>
+        <v>6764964</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3024,9 +3024,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3041,57 +3051,57 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130000797</v>
+        <v>130010447</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>78096</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6487</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>432910</v>
+        <v>432743</v>
       </c>
       <c r="R26" t="n">
-        <v>6764964</v>
+        <v>6764890</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3121,19 +3131,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3148,66 +3148,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130009984</v>
+        <v>130010439</v>
       </c>
       <c r="B27" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>432757</v>
+        <v>432941</v>
       </c>
       <c r="R27" t="n">
-        <v>6764953</v>
+        <v>6764955</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3237,50 +3228,39 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130009976</v>
+        <v>130010002</v>
       </c>
       <c r="B28" t="n">
-        <v>79678</v>
+        <v>79089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3288,21 +3268,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3312,10 +3292,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>432806</v>
+        <v>432842</v>
       </c>
       <c r="R28" t="n">
-        <v>6764957</v>
+        <v>6764945</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3347,7 +3327,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3357,7 +3337,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3384,10 +3364,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130010439</v>
+        <v>130000803</v>
       </c>
       <c r="B29" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3415,14 +3395,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>432941</v>
+        <v>433436</v>
       </c>
       <c r="R29" t="n">
-        <v>6764955</v>
+        <v>6765320</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3452,9 +3432,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3469,57 +3459,66 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130010002</v>
+        <v>130009984</v>
       </c>
       <c r="B30" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>432842</v>
+        <v>432757</v>
       </c>
       <c r="R30" t="n">
-        <v>6764945</v>
+        <v>6764953</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3551,7 +3550,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3561,7 +3560,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3570,6 +3569,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3588,10 +3588,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130000803</v>
+        <v>130009976</v>
       </c>
       <c r="B31" t="n">
-        <v>79088</v>
+        <v>79679</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3599,34 +3599,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433436</v>
+        <v>432806</v>
       </c>
       <c r="R31" t="n">
-        <v>6765320</v>
+        <v>6764957</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3683,22 +3683,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130009999</v>
+        <v>130010446</v>
       </c>
       <c r="B32" t="n">
-        <v>79088</v>
+        <v>78096</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3706,21 +3706,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3730,10 +3730,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>433404</v>
+        <v>432787</v>
       </c>
       <c r="R32" t="n">
-        <v>6765152</v>
+        <v>6764952</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3763,19 +3763,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3790,22 +3780,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130010440</v>
+        <v>130009999</v>
       </c>
       <c r="B33" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3837,10 +3827,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>432846</v>
+        <v>433404</v>
       </c>
       <c r="R33" t="n">
-        <v>6764945</v>
+        <v>6765152</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3870,9 +3860,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3887,22 +3887,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130010446</v>
+        <v>130010440</v>
       </c>
       <c r="B34" t="n">
-        <v>78095</v>
+        <v>79089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3910,21 +3910,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>432787</v>
+        <v>432846</v>
       </c>
       <c r="R34" t="n">
-        <v>6764952</v>
+        <v>6764945</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3996,10 +3996,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130009986</v>
+        <v>130009975</v>
       </c>
       <c r="B35" t="n">
-        <v>78845</v>
+        <v>79679</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4007,21 +4007,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4031,10 +4031,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>432880</v>
+        <v>432801</v>
       </c>
       <c r="R35" t="n">
-        <v>6764902</v>
+        <v>6765083</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4103,10 +4103,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130009975</v>
+        <v>130000795</v>
       </c>
       <c r="B36" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4134,14 +4134,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>432801</v>
+        <v>432795</v>
       </c>
       <c r="R36" t="n">
-        <v>6765083</v>
+        <v>6764980</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4198,22 +4198,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130000795</v>
+        <v>130009986</v>
       </c>
       <c r="B37" t="n">
-        <v>79678</v>
+        <v>78846</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4221,34 +4221,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>432795</v>
+        <v>432880</v>
       </c>
       <c r="R37" t="n">
-        <v>6764980</v>
+        <v>6764902</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4305,57 +4305,66 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130009980</v>
+        <v>130009982</v>
       </c>
       <c r="B38" t="n">
-        <v>90638</v>
+        <v>8451</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>433320</v>
+        <v>433497</v>
       </c>
       <c r="R38" t="n">
-        <v>6765160</v>
+        <v>6765321</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4387,7 +4396,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4397,7 +4406,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4425,10 +4434,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130010425</v>
+        <v>130009980</v>
       </c>
       <c r="B39" t="n">
-        <v>90638</v>
+        <v>90655</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4460,10 +4469,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>432853</v>
+        <v>433320</v>
       </c>
       <c r="R39" t="n">
-        <v>6765042</v>
+        <v>6765160</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4493,83 +4502,85 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130009982</v>
+        <v>130010425</v>
       </c>
       <c r="B40" t="n">
-        <v>8451</v>
+        <v>90655</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>1962</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>433497</v>
+        <v>432853</v>
       </c>
       <c r="R40" t="n">
-        <v>6765321</v>
+        <v>6765042</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4599,40 +4610,29 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4642,7 +4642,7 @@
         <v>130009998</v>
       </c>
       <c r="B41" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>130010442</v>
       </c>
       <c r="B42" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4843,45 +4843,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130010444</v>
+        <v>130000806</v>
       </c>
       <c r="B43" t="n">
-        <v>92888</v>
+        <v>79089</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>433284</v>
+        <v>432829</v>
       </c>
       <c r="R43" t="n">
-        <v>6765098</v>
+        <v>6765145</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4911,9 +4911,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4928,66 +4938,57 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130010429</v>
+        <v>130009993</v>
       </c>
       <c r="B44" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>432898</v>
+        <v>433494</v>
       </c>
       <c r="R44" t="n">
-        <v>6764968</v>
+        <v>6765320</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5017,30 +5018,39 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5050,7 +5060,7 @@
         <v>130000800</v>
       </c>
       <c r="B45" t="n">
-        <v>79089</v>
+        <v>79090</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5155,32 +5165,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130010424</v>
+        <v>130010444</v>
       </c>
       <c r="B46" t="n">
-        <v>90638</v>
+        <v>92905</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5190,10 +5200,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>433000</v>
+        <v>433284</v>
       </c>
       <c r="R46" t="n">
-        <v>6765168</v>
+        <v>6765098</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5252,10 +5262,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130000806</v>
+        <v>130010424</v>
       </c>
       <c r="B47" t="n">
-        <v>79088</v>
+        <v>90655</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5263,34 +5273,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>432829</v>
+        <v>433000</v>
       </c>
       <c r="R47" t="n">
-        <v>6765145</v>
+        <v>6765168</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5320,19 +5330,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5347,57 +5347,66 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130009993</v>
+        <v>130010429</v>
       </c>
       <c r="B48" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>433494</v>
+        <v>432898</v>
       </c>
       <c r="R48" t="n">
-        <v>6765320</v>
+        <v>6764968</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5427,84 +5436,79 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130009994</v>
+        <v>130000808</v>
       </c>
       <c r="B49" t="n">
-        <v>79088</v>
+        <v>92905</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>433500</v>
+        <v>432783</v>
       </c>
       <c r="R49" t="n">
-        <v>6765331</v>
+        <v>6765102</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5536,7 +5540,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5546,7 +5550,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5555,28 +5559,29 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130010441</v>
+        <v>130009994</v>
       </c>
       <c r="B50" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5608,10 +5613,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>432847</v>
+        <v>433500</v>
       </c>
       <c r="R50" t="n">
-        <v>6764943</v>
+        <v>6765331</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5641,9 +5646,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5658,61 +5673,57 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130000808</v>
+        <v>130010441</v>
       </c>
       <c r="B51" t="n">
-        <v>92888</v>
+        <v>79089</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>432783</v>
+        <v>432847</v>
       </c>
       <c r="R51" t="n">
-        <v>6765102</v>
+        <v>6764943</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5742,40 +5753,29 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5785,7 +5785,7 @@
         <v>130010438</v>
       </c>
       <c r="B52" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>130009978</v>
       </c>
       <c r="B53" t="n">
-        <v>91627</v>
+        <v>91644</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6115,32 +6115,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130010427</v>
+        <v>130010437</v>
       </c>
       <c r="B55" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6150,10 +6150,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>433049</v>
+        <v>433359</v>
       </c>
       <c r="R55" t="n">
-        <v>6765172</v>
+        <v>6765114</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6212,10 +6212,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130010423</v>
+        <v>130000802</v>
       </c>
       <c r="B56" t="n">
-        <v>79678</v>
+        <v>79089</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6223,34 +6223,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>432753</v>
+        <v>432785</v>
       </c>
       <c r="R56" t="n">
-        <v>6765037</v>
+        <v>6765104</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6280,9 +6280,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6297,22 +6307,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130010437</v>
+        <v>130010423</v>
       </c>
       <c r="B57" t="n">
-        <v>79088</v>
+        <v>79679</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6320,21 +6330,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6344,10 +6354,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>433359</v>
+        <v>432753</v>
       </c>
       <c r="R57" t="n">
-        <v>6765114</v>
+        <v>6765037</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6406,45 +6416,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130000802</v>
+        <v>130010427</v>
       </c>
       <c r="B58" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>432785</v>
+        <v>433049</v>
       </c>
       <c r="R58" t="n">
-        <v>6765104</v>
+        <v>6765172</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6474,19 +6484,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>14:54</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6501,22 +6501,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130009991</v>
+        <v>130010436</v>
       </c>
       <c r="B59" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>433469</v>
+        <v>433362</v>
       </c>
       <c r="R59" t="n">
-        <v>6765340</v>
+        <v>6765100</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6581,19 +6581,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>13:59</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6608,22 +6598,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130010000</v>
+        <v>130009989</v>
       </c>
       <c r="B60" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6655,10 +6645,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>432861</v>
+        <v>433473</v>
       </c>
       <c r="R60" t="n">
-        <v>6764984</v>
+        <v>6765313</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6690,7 +6680,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6700,7 +6690,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6727,10 +6717,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130010436</v>
+        <v>130009991</v>
       </c>
       <c r="B61" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6762,10 +6752,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>433362</v>
+        <v>433469</v>
       </c>
       <c r="R61" t="n">
-        <v>6765100</v>
+        <v>6765340</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6795,9 +6785,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6812,22 +6812,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130009989</v>
+        <v>130010000</v>
       </c>
       <c r="B62" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6859,10 +6859,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>433473</v>
+        <v>432861</v>
       </c>
       <c r="R62" t="n">
-        <v>6765313</v>
+        <v>6764984</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7048,54 +7048,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130010426</v>
+        <v>130010434</v>
       </c>
       <c r="B64" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>433443</v>
+        <v>433459</v>
       </c>
       <c r="R64" t="n">
-        <v>6765297</v>
+        <v>6765287</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7136,7 +7127,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7155,10 +7145,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130010434</v>
+        <v>130009979</v>
       </c>
       <c r="B65" t="n">
-        <v>79088</v>
+        <v>91644</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7166,21 +7156,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7190,10 +7180,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>433459</v>
+        <v>433285</v>
       </c>
       <c r="R65" t="n">
-        <v>6765287</v>
+        <v>6765090</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7223,9 +7213,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7240,12 +7240,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7255,7 +7255,7 @@
         <v>130010004</v>
       </c>
       <c r="B66" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7359,45 +7359,54 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130009979</v>
+        <v>130010426</v>
       </c>
       <c r="B67" t="n">
-        <v>91627</v>
+        <v>8451</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>433285</v>
+        <v>433443</v>
       </c>
       <c r="R67" t="n">
-        <v>6765090</v>
+        <v>6765297</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7427,39 +7436,30 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7469,7 +7469,7 @@
         <v>130009992</v>
       </c>
       <c r="B68" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>130009996</v>
       </c>
       <c r="B69" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>130010432</v>
       </c>
       <c r="B70" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>130010001</v>
       </c>
       <c r="B71" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7884,45 +7884,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130000796</v>
+        <v>130010433</v>
       </c>
       <c r="B72" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>433217</v>
+        <v>432809</v>
       </c>
       <c r="R72" t="n">
-        <v>6765206</v>
+        <v>6765129</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7952,19 +7952,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>12:40</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7979,22 +7969,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130010433</v>
+        <v>130010005</v>
       </c>
       <c r="B73" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8026,10 +8016,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432809</v>
+        <v>432732</v>
       </c>
       <c r="R73" t="n">
-        <v>6765129</v>
+        <v>6764932</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8059,9 +8049,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8076,57 +8076,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130010005</v>
+        <v>130000796</v>
       </c>
       <c r="B74" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>432732</v>
+        <v>433217</v>
       </c>
       <c r="R74" t="n">
-        <v>6764932</v>
+        <v>6765206</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8168,7 +8168,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8183,57 +8183,57 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130009990</v>
+        <v>130000798</v>
       </c>
       <c r="B75" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>433472</v>
+        <v>432873</v>
       </c>
       <c r="R75" t="n">
-        <v>6765327</v>
+        <v>6764999</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8290,22 +8290,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130010435</v>
+        <v>130009990</v>
       </c>
       <c r="B76" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8337,10 +8337,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>433498</v>
+        <v>433472</v>
       </c>
       <c r="R76" t="n">
-        <v>6765212</v>
+        <v>6765327</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8370,9 +8370,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8387,22 +8397,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130009988</v>
+        <v>130010435</v>
       </c>
       <c r="B77" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8434,10 +8444,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>433439</v>
+        <v>433498</v>
       </c>
       <c r="R77" t="n">
-        <v>6765313</v>
+        <v>6765212</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8467,19 +8477,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>14:09</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8494,57 +8494,57 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130000798</v>
+        <v>130009988</v>
       </c>
       <c r="B78" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>432873</v>
+        <v>433439</v>
       </c>
       <c r="R78" t="n">
-        <v>6764999</v>
+        <v>6765313</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8601,22 +8601,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130010003</v>
+        <v>130010445</v>
       </c>
       <c r="B79" t="n">
-        <v>79088</v>
+        <v>78096</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8624,21 +8624,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8648,10 +8648,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>432841</v>
+        <v>433119</v>
       </c>
       <c r="R79" t="n">
-        <v>6764949</v>
+        <v>6765204</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8681,19 +8681,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>10:55</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8708,22 +8698,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130010445</v>
+        <v>130010003</v>
       </c>
       <c r="B80" t="n">
-        <v>78095</v>
+        <v>79089</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8731,21 +8721,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8755,10 +8745,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>433119</v>
+        <v>432841</v>
       </c>
       <c r="R80" t="n">
-        <v>6765204</v>
+        <v>6764949</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8788,9 +8778,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8805,12 +8805,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9044,7 +9044,7 @@
         <v>129998689</v>
       </c>
       <c r="B83" t="n">
-        <v>91879</v>
+        <v>91896</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 56940-2025 artfynd.xlsx
+++ b/artfynd/A 56940-2025 artfynd.xlsx
@@ -3160,45 +3160,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130010439</v>
+        <v>130009984</v>
       </c>
       <c r="B27" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>432941</v>
+        <v>432757</v>
       </c>
       <c r="R27" t="n">
-        <v>6764955</v>
+        <v>6764953</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3228,36 +3237,47 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130010002</v>
+        <v>130010439</v>
       </c>
       <c r="B28" t="n">
         <v>79095</v>
@@ -3292,10 +3312,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>432842</v>
+        <v>432941</v>
       </c>
       <c r="R28" t="n">
-        <v>6764945</v>
+        <v>6764955</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3325,19 +3345,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>10:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3352,19 +3362,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130000803</v>
+        <v>130010002</v>
       </c>
       <c r="B29" t="n">
         <v>79095</v>
@@ -3395,14 +3405,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>433436</v>
+        <v>432842</v>
       </c>
       <c r="R29" t="n">
-        <v>6765320</v>
+        <v>6764945</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3434,7 +3444,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3444,7 +3454,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3459,22 +3469,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130009976</v>
+        <v>130000803</v>
       </c>
       <c r="B30" t="n">
-        <v>79685</v>
+        <v>79095</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3482,34 +3492,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>432806</v>
+        <v>433436</v>
       </c>
       <c r="R30" t="n">
-        <v>6764957</v>
+        <v>6765320</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3541,7 +3551,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3551,7 +3561,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3566,66 +3576,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130009984</v>
+        <v>130009976</v>
       </c>
       <c r="B31" t="n">
-        <v>8451</v>
+        <v>79685</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>432757</v>
+        <v>432806</v>
       </c>
       <c r="R31" t="n">
-        <v>6764953</v>
+        <v>6764957</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3657,7 +3658,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3667,7 +3668,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3676,7 +3677,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56940-2025 artfynd.xlsx
+++ b/artfynd/A 56940-2025 artfynd.xlsx
@@ -2235,32 +2235,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129998701</v>
+        <v>129998719</v>
       </c>
       <c r="B18" t="n">
-        <v>8451</v>
+        <v>79096</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>230405</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433145</v>
+        <v>432725</v>
       </c>
       <c r="R18" t="n">
-        <v>6765198</v>
+        <v>6764934</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2333,32 +2333,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129998719</v>
+        <v>129998701</v>
       </c>
       <c r="B19" t="n">
-        <v>79096</v>
+        <v>8451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>230405</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432725</v>
+        <v>433145</v>
       </c>
       <c r="R19" t="n">
-        <v>6764934</v>
+        <v>6765198</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2956,45 +2956,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130010447</v>
+        <v>130000797</v>
       </c>
       <c r="B25" t="n">
-        <v>78102</v>
+        <v>8451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6487</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>432743</v>
+        <v>432910</v>
       </c>
       <c r="R25" t="n">
-        <v>6764890</v>
+        <v>6764964</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3024,9 +3024,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3041,57 +3051,57 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130000797</v>
+        <v>130010447</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>78102</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6487</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>432910</v>
+        <v>432743</v>
       </c>
       <c r="R26" t="n">
-        <v>6764964</v>
+        <v>6764890</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3121,19 +3131,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3148,66 +3148,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130009984</v>
+        <v>130010439</v>
       </c>
       <c r="B27" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>432757</v>
+        <v>432941</v>
       </c>
       <c r="R27" t="n">
-        <v>6764953</v>
+        <v>6764955</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3237,47 +3228,36 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130010439</v>
+        <v>130010002</v>
       </c>
       <c r="B28" t="n">
         <v>79095</v>
@@ -3312,10 +3292,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>432941</v>
+        <v>432842</v>
       </c>
       <c r="R28" t="n">
-        <v>6764955</v>
+        <v>6764945</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3345,9 +3325,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3362,19 +3352,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130010002</v>
+        <v>130000803</v>
       </c>
       <c r="B29" t="n">
         <v>79095</v>
@@ -3405,14 +3395,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>432842</v>
+        <v>433436</v>
       </c>
       <c r="R29" t="n">
-        <v>6764945</v>
+        <v>6765320</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3444,7 +3434,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3454,7 +3444,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3469,57 +3459,66 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130000803</v>
+        <v>130009984</v>
       </c>
       <c r="B30" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>433436</v>
+        <v>432757</v>
       </c>
       <c r="R30" t="n">
-        <v>6765320</v>
+        <v>6764953</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3551,7 +3550,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3561,7 +3560,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3570,18 +3569,19 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3695,10 +3695,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130009999</v>
+        <v>130010446</v>
       </c>
       <c r="B32" t="n">
-        <v>79095</v>
+        <v>78102</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3706,21 +3706,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3730,10 +3730,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>433404</v>
+        <v>432787</v>
       </c>
       <c r="R32" t="n">
-        <v>6765152</v>
+        <v>6764952</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3763,19 +3763,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3790,19 +3780,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130010440</v>
+        <v>130009999</v>
       </c>
       <c r="B33" t="n">
         <v>79095</v>
@@ -3837,10 +3827,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>432846</v>
+        <v>433404</v>
       </c>
       <c r="R33" t="n">
-        <v>6764945</v>
+        <v>6765152</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3870,9 +3860,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3887,22 +3887,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130010446</v>
+        <v>130010440</v>
       </c>
       <c r="B34" t="n">
-        <v>78102</v>
+        <v>79095</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3910,21 +3910,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>432787</v>
+        <v>432846</v>
       </c>
       <c r="R34" t="n">
-        <v>6764952</v>
+        <v>6764945</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3996,10 +3996,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130009986</v>
+        <v>130009975</v>
       </c>
       <c r="B35" t="n">
-        <v>78852</v>
+        <v>79685</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4007,21 +4007,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4031,10 +4031,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>432880</v>
+        <v>432801</v>
       </c>
       <c r="R35" t="n">
-        <v>6764902</v>
+        <v>6765083</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4103,7 +4103,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130009975</v>
+        <v>130000795</v>
       </c>
       <c r="B36" t="n">
         <v>79685</v>
@@ -4134,14 +4134,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>432801</v>
+        <v>432795</v>
       </c>
       <c r="R36" t="n">
-        <v>6765083</v>
+        <v>6764980</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4198,22 +4198,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130000795</v>
+        <v>130009986</v>
       </c>
       <c r="B37" t="n">
-        <v>79685</v>
+        <v>78852</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4221,34 +4221,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>432795</v>
+        <v>432880</v>
       </c>
       <c r="R37" t="n">
-        <v>6764980</v>
+        <v>6764902</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4305,66 +4305,57 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130009982</v>
+        <v>130010425</v>
       </c>
       <c r="B38" t="n">
-        <v>8451</v>
+        <v>90671</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>1962</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>433497</v>
+        <v>432853</v>
       </c>
       <c r="R38" t="n">
-        <v>6765321</v>
+        <v>6765042</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4394,47 +4385,36 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130010425</v>
+        <v>130009980</v>
       </c>
       <c r="B39" t="n">
         <v>90671</v>
@@ -4469,10 +4449,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>432853</v>
+        <v>433320</v>
       </c>
       <c r="R39" t="n">
-        <v>6765042</v>
+        <v>6765160</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4502,74 +4482,94 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130009980</v>
+        <v>130009982</v>
       </c>
       <c r="B40" t="n">
-        <v>90671</v>
+        <v>8451</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>433320</v>
+        <v>433497</v>
       </c>
       <c r="R40" t="n">
-        <v>6765160</v>
+        <v>6765321</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4843,10 +4843,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130000806</v>
+        <v>130000800</v>
       </c>
       <c r="B43" t="n">
-        <v>79095</v>
+        <v>79096</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4854,16 +4854,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4878,10 +4878,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>432829</v>
+        <v>433464</v>
       </c>
       <c r="R43" t="n">
-        <v>6765145</v>
+        <v>6765289</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4932,6 +4932,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4950,10 +4951,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130009993</v>
+        <v>130010424</v>
       </c>
       <c r="B44" t="n">
-        <v>79095</v>
+        <v>90671</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4961,21 +4962,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4985,10 +4986,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>433494</v>
+        <v>433000</v>
       </c>
       <c r="R44" t="n">
-        <v>6765320</v>
+        <v>6765168</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5018,19 +5019,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:58</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5045,44 +5036,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130010424</v>
+        <v>130010444</v>
       </c>
       <c r="B45" t="n">
-        <v>90671</v>
+        <v>92921</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5092,10 +5083,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>433000</v>
+        <v>433284</v>
       </c>
       <c r="R45" t="n">
-        <v>6765168</v>
+        <v>6765098</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5154,45 +5145,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130010444</v>
+        <v>130000806</v>
       </c>
       <c r="B46" t="n">
-        <v>92921</v>
+        <v>79095</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>433284</v>
+        <v>432829</v>
       </c>
       <c r="R46" t="n">
-        <v>6765098</v>
+        <v>6765145</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5222,9 +5213,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5239,66 +5240,57 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130010429</v>
+        <v>130009993</v>
       </c>
       <c r="B47" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>432898</v>
+        <v>433494</v>
       </c>
       <c r="R47" t="n">
-        <v>6764968</v>
+        <v>6765320</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5328,75 +5320,93 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130000800</v>
+        <v>130010429</v>
       </c>
       <c r="B48" t="n">
-        <v>79096</v>
+        <v>8451</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>230405</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>433464</v>
+        <v>432898</v>
       </c>
       <c r="R48" t="n">
-        <v>6765289</v>
+        <v>6764968</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5426,19 +5436,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:57</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5454,12 +5454,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>

--- a/artfynd/A 56940-2025 artfynd.xlsx
+++ b/artfynd/A 56940-2025 artfynd.xlsx
@@ -2133,32 +2133,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129998690</v>
+        <v>129998701</v>
       </c>
       <c r="B17" t="n">
-        <v>91660</v>
+        <v>8451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433075</v>
+        <v>433145</v>
       </c>
       <c r="R17" t="n">
-        <v>6765183</v>
+        <v>6765198</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2206,17 +2206,13 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>1 st. Inte samma träd som tickorna bredvid.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2235,10 +2231,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129998719</v>
+        <v>129998690</v>
       </c>
       <c r="B18" t="n">
-        <v>79096</v>
+        <v>91662</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2246,21 +2242,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>230405</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2270,10 +2266,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>432725</v>
+        <v>433075</v>
       </c>
       <c r="R18" t="n">
-        <v>6764934</v>
+        <v>6765183</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2308,13 +2304,17 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1 st. Inte samma träd som tickorna bredvid.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2333,32 +2333,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129998701</v>
+        <v>129998719</v>
       </c>
       <c r="B19" t="n">
-        <v>8451</v>
+        <v>79096</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>230405</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433145</v>
+        <v>432725</v>
       </c>
       <c r="R19" t="n">
-        <v>6765198</v>
+        <v>6764934</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130009997</v>
+        <v>130010431</v>
       </c>
       <c r="B20" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2442,21 +2442,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433474</v>
+        <v>432755</v>
       </c>
       <c r="R20" t="n">
-        <v>6765288</v>
+        <v>6764944</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2499,19 +2499,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2526,19 +2516,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130009995</v>
+        <v>130009997</v>
       </c>
       <c r="B21" t="n">
         <v>79095</v>
@@ -2573,10 +2563,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433498</v>
+        <v>433474</v>
       </c>
       <c r="R21" t="n">
-        <v>6765316</v>
+        <v>6765288</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2608,7 +2598,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2618,7 +2608,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2645,10 +2635,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130010431</v>
+        <v>130009995</v>
       </c>
       <c r="B22" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2656,21 +2646,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2680,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>432755</v>
+        <v>433498</v>
       </c>
       <c r="R22" t="n">
-        <v>6764944</v>
+        <v>6765316</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2713,9 +2703,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2730,12 +2730,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130000805</v>
+        <v>130010447</v>
       </c>
       <c r="B24" t="n">
-        <v>79095</v>
+        <v>78102</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2860,34 +2860,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>432810</v>
+        <v>432743</v>
       </c>
       <c r="R24" t="n">
-        <v>6765134</v>
+        <v>6764890</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2917,19 +2917,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>12:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2944,44 +2934,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130000797</v>
+        <v>130000805</v>
       </c>
       <c r="B25" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2991,10 +2981,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>432910</v>
+        <v>432810</v>
       </c>
       <c r="R25" t="n">
-        <v>6764964</v>
+        <v>6765134</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3026,7 +3016,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3036,7 +3026,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3063,45 +3053,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130010447</v>
+        <v>130000797</v>
       </c>
       <c r="B26" t="n">
-        <v>78102</v>
+        <v>8451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6487</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>432743</v>
+        <v>432910</v>
       </c>
       <c r="R26" t="n">
-        <v>6764890</v>
+        <v>6764964</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3131,9 +3121,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3148,12 +3148,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3257,10 +3257,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130010002</v>
+        <v>130009976</v>
       </c>
       <c r="B28" t="n">
-        <v>79095</v>
+        <v>79685</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3268,21 +3268,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>432842</v>
+        <v>432806</v>
       </c>
       <c r="R28" t="n">
-        <v>6764945</v>
+        <v>6764957</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3364,7 +3364,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130000803</v>
+        <v>130010002</v>
       </c>
       <c r="B29" t="n">
         <v>79095</v>
@@ -3395,14 +3395,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>433436</v>
+        <v>432842</v>
       </c>
       <c r="R29" t="n">
-        <v>6765320</v>
+        <v>6764945</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3459,66 +3459,57 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130009984</v>
+        <v>130000803</v>
       </c>
       <c r="B30" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>432757</v>
+        <v>433436</v>
       </c>
       <c r="R30" t="n">
-        <v>6764953</v>
+        <v>6765320</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3550,7 +3541,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3560,7 +3551,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3569,64 +3560,72 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130009976</v>
+        <v>130009984</v>
       </c>
       <c r="B31" t="n">
-        <v>79685</v>
+        <v>8451</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>432806</v>
+        <v>432757</v>
       </c>
       <c r="R31" t="n">
-        <v>6764957</v>
+        <v>6764953</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3658,7 +3657,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3668,7 +3667,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3677,6 +3676,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4317,10 +4317,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130010425</v>
+        <v>130009980</v>
       </c>
       <c r="B38" t="n">
-        <v>90671</v>
+        <v>90673</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>432853</v>
+        <v>433320</v>
       </c>
       <c r="R38" t="n">
-        <v>6765042</v>
+        <v>6765160</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4385,39 +4385,50 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130009980</v>
+        <v>130010425</v>
       </c>
       <c r="B39" t="n">
-        <v>90671</v>
+        <v>90673</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4449,10 +4460,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>433320</v>
+        <v>432853</v>
       </c>
       <c r="R39" t="n">
-        <v>6765160</v>
+        <v>6765042</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4482,40 +4493,29 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4639,7 +4639,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130009998</v>
+        <v>130010442</v>
       </c>
       <c r="B41" t="n">
         <v>79095</v>
@@ -4674,10 +4674,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>433400</v>
+        <v>432625</v>
       </c>
       <c r="R41" t="n">
-        <v>6765137</v>
+        <v>6764870</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4707,19 +4707,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4734,19 +4724,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130010442</v>
+        <v>130009998</v>
       </c>
       <c r="B42" t="n">
         <v>79095</v>
@@ -4781,10 +4771,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>432625</v>
+        <v>433400</v>
       </c>
       <c r="R42" t="n">
-        <v>6764870</v>
+        <v>6765137</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4814,9 +4804,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4831,57 +4831,57 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130000800</v>
+        <v>130010444</v>
       </c>
       <c r="B43" t="n">
-        <v>79096</v>
+        <v>92923</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>230405</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>433464</v>
+        <v>433284</v>
       </c>
       <c r="R43" t="n">
-        <v>6765289</v>
+        <v>6765098</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4911,40 +4911,29 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -4954,7 +4943,7 @@
         <v>130010424</v>
       </c>
       <c r="B44" t="n">
-        <v>90671</v>
+        <v>90673</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5048,45 +5037,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130010444</v>
+        <v>130000806</v>
       </c>
       <c r="B45" t="n">
-        <v>92921</v>
+        <v>79095</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>433284</v>
+        <v>432829</v>
       </c>
       <c r="R45" t="n">
-        <v>6765098</v>
+        <v>6765145</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5116,9 +5105,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5133,19 +5132,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130000806</v>
+        <v>130009993</v>
       </c>
       <c r="B46" t="n">
         <v>79095</v>
@@ -5176,14 +5175,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>432829</v>
+        <v>433494</v>
       </c>
       <c r="R46" t="n">
-        <v>6765145</v>
+        <v>6765320</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5215,7 +5214,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5225,7 +5224,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5240,57 +5239,66 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130009993</v>
+        <v>130010429</v>
       </c>
       <c r="B47" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>433494</v>
+        <v>432898</v>
       </c>
       <c r="R47" t="n">
-        <v>6765320</v>
+        <v>6764968</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5320,93 +5328,75 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130010429</v>
+        <v>130000800</v>
       </c>
       <c r="B48" t="n">
-        <v>8451</v>
+        <v>79096</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>230405</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>432898</v>
+        <v>433464</v>
       </c>
       <c r="R48" t="n">
-        <v>6764968</v>
+        <v>6765289</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5436,9 +5426,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5454,61 +5454,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130000808</v>
+        <v>130009994</v>
       </c>
       <c r="B49" t="n">
-        <v>92921</v>
+        <v>79095</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>432783</v>
+        <v>433500</v>
       </c>
       <c r="R49" t="n">
-        <v>6765102</v>
+        <v>6765331</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5540,7 +5536,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5550,7 +5546,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5559,26 +5555,25 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130009994</v>
+        <v>130010441</v>
       </c>
       <c r="B50" t="n">
         <v>79095</v>
@@ -5613,10 +5608,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>433500</v>
+        <v>432847</v>
       </c>
       <c r="R50" t="n">
-        <v>6765331</v>
+        <v>6764943</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5646,19 +5641,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>13:57</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5673,57 +5658,61 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130010441</v>
+        <v>130000808</v>
       </c>
       <c r="B51" t="n">
-        <v>79095</v>
+        <v>92923</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>432847</v>
+        <v>432783</v>
       </c>
       <c r="R51" t="n">
-        <v>6764943</v>
+        <v>6765102</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5753,29 +5742,40 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5882,7 +5882,7 @@
         <v>130009978</v>
       </c>
       <c r="B53" t="n">
-        <v>91660</v>
+        <v>91662</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6115,32 +6115,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130010437</v>
+        <v>130010427</v>
       </c>
       <c r="B55" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6150,10 +6150,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>433359</v>
+        <v>433049</v>
       </c>
       <c r="R55" t="n">
-        <v>6765114</v>
+        <v>6765172</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6212,7 +6212,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130000802</v>
+        <v>130010437</v>
       </c>
       <c r="B56" t="n">
         <v>79095</v>
@@ -6243,14 +6243,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>432785</v>
+        <v>433359</v>
       </c>
       <c r="R56" t="n">
-        <v>6765104</v>
+        <v>6765114</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6280,19 +6280,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>14:54</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6307,44 +6297,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130010427</v>
+        <v>130010423</v>
       </c>
       <c r="B57" t="n">
-        <v>8451</v>
+        <v>79685</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6354,10 +6344,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>433049</v>
+        <v>432753</v>
       </c>
       <c r="R57" t="n">
-        <v>6765172</v>
+        <v>6765037</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6416,10 +6406,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130010423</v>
+        <v>130000802</v>
       </c>
       <c r="B58" t="n">
-        <v>79685</v>
+        <v>79095</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6427,34 +6417,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>432753</v>
+        <v>432785</v>
       </c>
       <c r="R58" t="n">
-        <v>6765037</v>
+        <v>6765104</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6484,9 +6474,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6501,12 +6501,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7048,10 +7048,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130010434</v>
+        <v>130009979</v>
       </c>
       <c r="B64" t="n">
-        <v>79095</v>
+        <v>91662</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7059,21 +7059,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>433459</v>
+        <v>433285</v>
       </c>
       <c r="R64" t="n">
-        <v>6765287</v>
+        <v>6765090</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7116,9 +7116,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7133,19 +7143,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130010004</v>
+        <v>130010434</v>
       </c>
       <c r="B65" t="n">
         <v>79095</v>
@@ -7180,10 +7190,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432836</v>
+        <v>433459</v>
       </c>
       <c r="R65" t="n">
-        <v>6764947</v>
+        <v>6765287</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7213,19 +7223,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>10:53</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7240,66 +7240,57 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130010426</v>
+        <v>130010004</v>
       </c>
       <c r="B66" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>433443</v>
+        <v>432836</v>
       </c>
       <c r="R66" t="n">
-        <v>6765297</v>
+        <v>6764947</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7329,75 +7320,93 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130009979</v>
+        <v>130010426</v>
       </c>
       <c r="B67" t="n">
-        <v>91660</v>
+        <v>8451</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>433285</v>
+        <v>433443</v>
       </c>
       <c r="R67" t="n">
-        <v>6765090</v>
+        <v>6765297</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7427,39 +7436,30 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7884,45 +7884,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130000796</v>
+        <v>130010433</v>
       </c>
       <c r="B72" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>433217</v>
+        <v>432809</v>
       </c>
       <c r="R72" t="n">
-        <v>6765206</v>
+        <v>6765129</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7952,19 +7952,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>12:40</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7979,19 +7969,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130010433</v>
+        <v>130010005</v>
       </c>
       <c r="B73" t="n">
         <v>79095</v>
@@ -8026,10 +8016,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432809</v>
+        <v>432732</v>
       </c>
       <c r="R73" t="n">
-        <v>6765129</v>
+        <v>6764932</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8059,9 +8049,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8076,57 +8076,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130010005</v>
+        <v>130000796</v>
       </c>
       <c r="B74" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>432732</v>
+        <v>433217</v>
       </c>
       <c r="R74" t="n">
-        <v>6764932</v>
+        <v>6765206</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8168,7 +8168,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8183,12 +8183,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8302,7 +8302,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130010435</v>
+        <v>130009988</v>
       </c>
       <c r="B76" t="n">
         <v>79095</v>
@@ -8337,10 +8337,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>433498</v>
+        <v>433439</v>
       </c>
       <c r="R76" t="n">
-        <v>6765212</v>
+        <v>6765313</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8370,9 +8370,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8387,57 +8397,57 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130009988</v>
+        <v>130000798</v>
       </c>
       <c r="B77" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>433439</v>
+        <v>432873</v>
       </c>
       <c r="R77" t="n">
-        <v>6765313</v>
+        <v>6764999</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8469,7 +8479,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8479,7 +8489,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8494,57 +8504,57 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130000798</v>
+        <v>130010435</v>
       </c>
       <c r="B78" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>432873</v>
+        <v>433498</v>
       </c>
       <c r="R78" t="n">
-        <v>6764999</v>
+        <v>6765212</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8574,19 +8584,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8601,22 +8601,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130010003</v>
+        <v>130010445</v>
       </c>
       <c r="B79" t="n">
-        <v>79095</v>
+        <v>78102</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8624,21 +8624,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8648,10 +8648,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>432841</v>
+        <v>433119</v>
       </c>
       <c r="R79" t="n">
-        <v>6764949</v>
+        <v>6765204</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8681,19 +8681,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>10:55</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8708,22 +8698,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130010445</v>
+        <v>130010003</v>
       </c>
       <c r="B80" t="n">
-        <v>78102</v>
+        <v>79095</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8731,21 +8721,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8755,10 +8745,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>433119</v>
+        <v>432841</v>
       </c>
       <c r="R80" t="n">
-        <v>6765204</v>
+        <v>6764949</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8788,9 +8778,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8805,12 +8805,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9044,7 +9044,7 @@
         <v>129998689</v>
       </c>
       <c r="B83" t="n">
-        <v>91912</v>
+        <v>91914</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 56940-2025 artfynd.xlsx
+++ b/artfynd/A 56940-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129998685</v>
       </c>
       <c r="B2" t="n">
-        <v>79685</v>
+        <v>79770</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129998684</v>
       </c>
       <c r="B3" t="n">
-        <v>79685</v>
+        <v>79770</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129998703</v>
+        <v>129998697</v>
       </c>
       <c r="B4" t="n">
-        <v>8451</v>
+        <v>78938</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432909</v>
+        <v>433506</v>
       </c>
       <c r="R4" t="n">
-        <v>6765182</v>
+        <v>6765247</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129998697</v>
+        <v>129998703</v>
       </c>
       <c r="B5" t="n">
-        <v>78853</v>
+        <v>8451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>433506</v>
+        <v>432909</v>
       </c>
       <c r="R5" t="n">
-        <v>6765247</v>
+        <v>6765182</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1066,7 +1066,7 @@
         <v>129998708</v>
       </c>
       <c r="B6" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129998686</v>
       </c>
       <c r="B7" t="n">
-        <v>79685</v>
+        <v>79770</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129998718</v>
       </c>
       <c r="B9" t="n">
-        <v>79096</v>
+        <v>79181</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>129998683</v>
       </c>
       <c r="B10" t="n">
-        <v>79685</v>
+        <v>79770</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1549,32 +1549,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129998717</v>
+        <v>129998704</v>
       </c>
       <c r="B11" t="n">
-        <v>79096</v>
+        <v>8451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>230405</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433514</v>
+        <v>432886</v>
       </c>
       <c r="R11" t="n">
-        <v>6765225</v>
+        <v>6765067</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1628,7 +1628,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1647,32 +1646,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129998704</v>
+        <v>129998717</v>
       </c>
       <c r="B12" t="n">
-        <v>8451</v>
+        <v>79181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>230405</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1682,10 +1681,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432886</v>
+        <v>433514</v>
       </c>
       <c r="R12" t="n">
-        <v>6765067</v>
+        <v>6765225</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1726,6 +1725,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1747,7 +1747,7 @@
         <v>129998698</v>
       </c>
       <c r="B13" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129998687</v>
       </c>
       <c r="B14" t="n">
-        <v>79685</v>
+        <v>79770</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>129998716</v>
       </c>
       <c r="B15" t="n">
-        <v>79096</v>
+        <v>79181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>129998688</v>
       </c>
       <c r="B16" t="n">
-        <v>79685</v>
+        <v>79770</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2231,10 +2231,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129998690</v>
+        <v>129998719</v>
       </c>
       <c r="B18" t="n">
-        <v>91662</v>
+        <v>79181</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2242,21 +2242,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>230405</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433075</v>
+        <v>432725</v>
       </c>
       <c r="R18" t="n">
-        <v>6765183</v>
+        <v>6764934</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2304,17 +2304,13 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>1 st. Inte samma träd som tickorna bredvid.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2333,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129998719</v>
+        <v>129998690</v>
       </c>
       <c r="B19" t="n">
-        <v>79096</v>
+        <v>91749</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,21 +2340,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>230405</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432725</v>
+        <v>433075</v>
       </c>
       <c r="R19" t="n">
-        <v>6764934</v>
+        <v>6765183</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2406,13 +2402,17 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>1 st. Inte samma träd som tickorna bredvid.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130010431</v>
+        <v>130009997</v>
       </c>
       <c r="B20" t="n">
-        <v>78852</v>
+        <v>79180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2442,21 +2442,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>432755</v>
+        <v>433474</v>
       </c>
       <c r="R20" t="n">
-        <v>6764944</v>
+        <v>6765288</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2499,9 +2499,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2516,22 +2526,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130009997</v>
+        <v>130009995</v>
       </c>
       <c r="B21" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2563,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433474</v>
+        <v>433498</v>
       </c>
       <c r="R21" t="n">
-        <v>6765288</v>
+        <v>6765316</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2598,7 +2608,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2608,7 +2618,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2635,45 +2645,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130009995</v>
+        <v>130010428</v>
       </c>
       <c r="B22" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>433498</v>
+        <v>432868</v>
       </c>
       <c r="R22" t="n">
-        <v>6765316</v>
+        <v>6764991</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2703,93 +2722,75 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130010428</v>
+        <v>130010431</v>
       </c>
       <c r="B23" t="n">
-        <v>8451</v>
+        <v>78937</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>432868</v>
+        <v>432755</v>
       </c>
       <c r="R23" t="n">
-        <v>6764991</v>
+        <v>6764944</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2830,7 +2831,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2849,45 +2849,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130010447</v>
+        <v>130000797</v>
       </c>
       <c r="B24" t="n">
-        <v>78102</v>
+        <v>8451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6487</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>432743</v>
+        <v>432910</v>
       </c>
       <c r="R24" t="n">
-        <v>6764890</v>
+        <v>6764964</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2917,9 +2917,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2934,12 +2944,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -2949,7 +2959,7 @@
         <v>130000805</v>
       </c>
       <c r="B25" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3053,45 +3063,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130000797</v>
+        <v>130010447</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>78187</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6487</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>432910</v>
+        <v>432743</v>
       </c>
       <c r="R26" t="n">
-        <v>6764964</v>
+        <v>6764890</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3121,19 +3131,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3148,22 +3148,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130010439</v>
+        <v>130010002</v>
       </c>
       <c r="B27" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>432941</v>
+        <v>432842</v>
       </c>
       <c r="R27" t="n">
-        <v>6764955</v>
+        <v>6764945</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3228,9 +3228,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3245,57 +3255,66 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130009976</v>
+        <v>130009984</v>
       </c>
       <c r="B28" t="n">
-        <v>79685</v>
+        <v>8451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>432806</v>
+        <v>432757</v>
       </c>
       <c r="R28" t="n">
-        <v>6764957</v>
+        <v>6764953</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3327,7 +3346,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3337,7 +3356,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3346,6 +3365,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3364,10 +3384,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130010002</v>
+        <v>130009976</v>
       </c>
       <c r="B29" t="n">
-        <v>79095</v>
+        <v>79770</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3375,21 +3395,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3399,10 +3419,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>432842</v>
+        <v>432806</v>
       </c>
       <c r="R29" t="n">
-        <v>6764945</v>
+        <v>6764957</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3434,7 +3454,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3444,7 +3464,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3471,10 +3491,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130000803</v>
+        <v>130010439</v>
       </c>
       <c r="B30" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3502,14 +3522,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>433436</v>
+        <v>432941</v>
       </c>
       <c r="R30" t="n">
-        <v>6765320</v>
+        <v>6764955</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3539,19 +3559,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3566,66 +3576,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130009984</v>
+        <v>130000803</v>
       </c>
       <c r="B31" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>432757</v>
+        <v>433436</v>
       </c>
       <c r="R31" t="n">
-        <v>6764953</v>
+        <v>6765320</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3657,7 +3658,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3667,7 +3668,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3676,19 +3677,18 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3698,7 +3698,7 @@
         <v>130010446</v>
       </c>
       <c r="B32" t="n">
-        <v>78102</v>
+        <v>78187</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3792,10 +3792,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130009999</v>
+        <v>130010440</v>
       </c>
       <c r="B33" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>433404</v>
+        <v>432846</v>
       </c>
       <c r="R33" t="n">
-        <v>6765152</v>
+        <v>6764945</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3860,19 +3860,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3887,22 +3877,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130010440</v>
+        <v>130009999</v>
       </c>
       <c r="B34" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3934,10 +3924,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>432846</v>
+        <v>433404</v>
       </c>
       <c r="R34" t="n">
-        <v>6764945</v>
+        <v>6765152</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3967,9 +3957,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3984,22 +3984,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130009975</v>
+        <v>130000795</v>
       </c>
       <c r="B35" t="n">
-        <v>79685</v>
+        <v>79770</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4027,14 +4027,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>432801</v>
+        <v>432795</v>
       </c>
       <c r="R35" t="n">
-        <v>6765083</v>
+        <v>6764980</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4091,22 +4091,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130000795</v>
+        <v>130009975</v>
       </c>
       <c r="B36" t="n">
-        <v>79685</v>
+        <v>79770</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4134,14 +4134,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>432795</v>
+        <v>432801</v>
       </c>
       <c r="R36" t="n">
-        <v>6764980</v>
+        <v>6765083</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4198,12 +4198,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4213,7 +4213,7 @@
         <v>130009986</v>
       </c>
       <c r="B37" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>130009980</v>
       </c>
       <c r="B38" t="n">
-        <v>90673</v>
+        <v>90760</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4425,45 +4425,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130010425</v>
+        <v>130009982</v>
       </c>
       <c r="B39" t="n">
-        <v>90673</v>
+        <v>8451</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>432853</v>
+        <v>433497</v>
       </c>
       <c r="R39" t="n">
-        <v>6765042</v>
+        <v>6765321</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4493,83 +4502,85 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130009982</v>
+        <v>130010425</v>
       </c>
       <c r="B40" t="n">
-        <v>8451</v>
+        <v>90760</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>1962</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>433497</v>
+        <v>432853</v>
       </c>
       <c r="R40" t="n">
-        <v>6765321</v>
+        <v>6765042</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4599,50 +4610,39 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130010442</v>
+        <v>130009998</v>
       </c>
       <c r="B41" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4674,10 +4674,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>432625</v>
+        <v>433400</v>
       </c>
       <c r="R41" t="n">
-        <v>6764870</v>
+        <v>6765137</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4707,9 +4707,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4724,22 +4734,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130009998</v>
+        <v>130010442</v>
       </c>
       <c r="B42" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4771,10 +4781,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>433400</v>
+        <v>432625</v>
       </c>
       <c r="R42" t="n">
-        <v>6765137</v>
+        <v>6764870</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4804,19 +4814,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4831,57 +4831,57 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130010444</v>
+        <v>130000800</v>
       </c>
       <c r="B43" t="n">
-        <v>92923</v>
+        <v>79181</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>230405</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>433284</v>
+        <v>433464</v>
       </c>
       <c r="R43" t="n">
-        <v>6765098</v>
+        <v>6765289</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4911,39 +4911,50 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130010424</v>
+        <v>130000806</v>
       </c>
       <c r="B44" t="n">
-        <v>90673</v>
+        <v>79180</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4951,34 +4962,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>433000</v>
+        <v>432829</v>
       </c>
       <c r="R44" t="n">
-        <v>6765168</v>
+        <v>6765145</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5008,9 +5019,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5025,57 +5046,66 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130000806</v>
+        <v>130010429</v>
       </c>
       <c r="B45" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>432829</v>
+        <v>432898</v>
       </c>
       <c r="R45" t="n">
-        <v>6765145</v>
+        <v>6764968</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5105,39 +5135,30 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5147,7 +5168,7 @@
         <v>130009993</v>
       </c>
       <c r="B46" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5251,10 +5272,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130010429</v>
+        <v>130010444</v>
       </c>
       <c r="B47" t="n">
-        <v>8451</v>
+        <v>93010</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5262,43 +5283,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>432898</v>
+        <v>433284</v>
       </c>
       <c r="R47" t="n">
-        <v>6764968</v>
+        <v>6765098</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5339,7 +5351,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5358,10 +5369,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130000800</v>
+        <v>130010424</v>
       </c>
       <c r="B48" t="n">
-        <v>79096</v>
+        <v>90760</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5369,34 +5380,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>230405</v>
+        <v>1962</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>433464</v>
+        <v>433000</v>
       </c>
       <c r="R48" t="n">
-        <v>6765289</v>
+        <v>6765168</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5426,40 +5437,29 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5469,7 +5469,7 @@
         <v>130009994</v>
       </c>
       <c r="B49" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>130010441</v>
       </c>
       <c r="B50" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>130000808</v>
       </c>
       <c r="B51" t="n">
-        <v>92923</v>
+        <v>93010</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>130010438</v>
       </c>
       <c r="B52" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>130009978</v>
       </c>
       <c r="B53" t="n">
-        <v>91662</v>
+        <v>91749</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6115,32 +6115,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130010427</v>
+        <v>130010423</v>
       </c>
       <c r="B55" t="n">
-        <v>8451</v>
+        <v>79770</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6150,10 +6150,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>433049</v>
+        <v>432753</v>
       </c>
       <c r="R55" t="n">
-        <v>6765172</v>
+        <v>6765037</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6212,32 +6212,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130010437</v>
+        <v>130010427</v>
       </c>
       <c r="B56" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>433359</v>
+        <v>433049</v>
       </c>
       <c r="R56" t="n">
-        <v>6765114</v>
+        <v>6765172</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6309,10 +6309,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130010423</v>
+        <v>130010437</v>
       </c>
       <c r="B57" t="n">
-        <v>79685</v>
+        <v>79180</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6320,21 +6320,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>432753</v>
+        <v>433359</v>
       </c>
       <c r="R57" t="n">
-        <v>6765037</v>
+        <v>6765114</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6409,7 +6409,7 @@
         <v>130000802</v>
       </c>
       <c r="B58" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6513,54 +6513,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130009981</v>
+        <v>130009989</v>
       </c>
       <c r="B59" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>433429</v>
+        <v>433473</v>
       </c>
       <c r="R59" t="n">
-        <v>6765324</v>
+        <v>6765313</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6592,7 +6583,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6602,7 +6593,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6611,7 +6602,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6630,45 +6620,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130010436</v>
+        <v>130009981</v>
       </c>
       <c r="B60" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>433362</v>
+        <v>433429</v>
       </c>
       <c r="R60" t="n">
-        <v>6765100</v>
+        <v>6765324</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6698,39 +6697,50 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130009989</v>
+        <v>130009991</v>
       </c>
       <c r="B61" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6762,10 +6772,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>433473</v>
+        <v>433469</v>
       </c>
       <c r="R61" t="n">
-        <v>6765313</v>
+        <v>6765340</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6797,7 +6807,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6807,7 +6817,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6834,10 +6844,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130009991</v>
+        <v>130010000</v>
       </c>
       <c r="B62" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6869,10 +6879,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>433469</v>
+        <v>432861</v>
       </c>
       <c r="R62" t="n">
-        <v>6765340</v>
+        <v>6764984</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6904,7 +6914,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -6914,7 +6924,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6941,10 +6951,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130010000</v>
+        <v>130010436</v>
       </c>
       <c r="B63" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6976,10 +6986,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>432861</v>
+        <v>433362</v>
       </c>
       <c r="R63" t="n">
-        <v>6764984</v>
+        <v>6765100</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7009,19 +7019,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:44</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7036,12 +7036,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7051,7 +7051,7 @@
         <v>130009979</v>
       </c>
       <c r="B64" t="n">
-        <v>91662</v>
+        <v>91749</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130010434</v>
+        <v>130010004</v>
       </c>
       <c r="B65" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7190,10 +7190,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>433459</v>
+        <v>432836</v>
       </c>
       <c r="R65" t="n">
-        <v>6765287</v>
+        <v>6764947</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7223,9 +7223,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7240,22 +7250,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130010004</v>
+        <v>130010434</v>
       </c>
       <c r="B66" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7287,10 +7297,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>432836</v>
+        <v>433459</v>
       </c>
       <c r="R66" t="n">
-        <v>6764947</v>
+        <v>6765287</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7320,19 +7330,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>10:53</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7347,12 +7347,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7469,7 +7469,7 @@
         <v>130009992</v>
       </c>
       <c r="B68" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>130009996</v>
       </c>
       <c r="B69" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7680,10 +7680,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130010432</v>
+        <v>130010001</v>
       </c>
       <c r="B70" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7715,10 +7715,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>432782</v>
+        <v>432965</v>
       </c>
       <c r="R70" t="n">
-        <v>6765113</v>
+        <v>6764935</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7748,9 +7748,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7765,22 +7775,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130010001</v>
+        <v>130010432</v>
       </c>
       <c r="B71" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7812,10 +7822,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>432965</v>
+        <v>432782</v>
       </c>
       <c r="R71" t="n">
-        <v>6764935</v>
+        <v>6765113</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7845,19 +7855,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>11:24</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7872,57 +7872,57 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130010433</v>
+        <v>130000796</v>
       </c>
       <c r="B72" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>432809</v>
+        <v>433217</v>
       </c>
       <c r="R72" t="n">
-        <v>6765129</v>
+        <v>6765206</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7952,9 +7952,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7969,12 +7979,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -7984,7 +7994,7 @@
         <v>130010005</v>
       </c>
       <c r="B73" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8088,45 +8098,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130000796</v>
+        <v>130010433</v>
       </c>
       <c r="B74" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>433217</v>
+        <v>432809</v>
       </c>
       <c r="R74" t="n">
-        <v>6765206</v>
+        <v>6765129</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8156,19 +8166,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>12:40</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8183,12 +8183,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8198,7 +8198,7 @@
         <v>130009990</v>
       </c>
       <c r="B75" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>130009988</v>
       </c>
       <c r="B76" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8409,45 +8409,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130000798</v>
+        <v>130010435</v>
       </c>
       <c r="B77" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>432873</v>
+        <v>433498</v>
       </c>
       <c r="R77" t="n">
-        <v>6764999</v>
+        <v>6765212</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8477,19 +8477,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8504,57 +8494,57 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130010435</v>
+        <v>130000798</v>
       </c>
       <c r="B78" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>433498</v>
+        <v>432873</v>
       </c>
       <c r="R78" t="n">
-        <v>6765212</v>
+        <v>6764999</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8584,9 +8574,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8601,12 +8601,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8616,7 +8616,7 @@
         <v>130010445</v>
       </c>
       <c r="B79" t="n">
-        <v>78102</v>
+        <v>78187</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>130010003</v>
       </c>
       <c r="B80" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>129998689</v>
       </c>
       <c r="B83" t="n">
-        <v>91914</v>
+        <v>92001</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 56940-2025 artfynd.xlsx
+++ b/artfynd/A 56940-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129998697</v>
+        <v>129998703</v>
       </c>
       <c r="B4" t="n">
-        <v>78938</v>
+        <v>8451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433506</v>
+        <v>432909</v>
       </c>
       <c r="R4" t="n">
-        <v>6765247</v>
+        <v>6765182</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129998703</v>
+        <v>129998697</v>
       </c>
       <c r="B5" t="n">
-        <v>8451</v>
+        <v>78938</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432909</v>
+        <v>433506</v>
       </c>
       <c r="R5" t="n">
-        <v>6765182</v>
+        <v>6765247</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130009997</v>
+        <v>130010431</v>
       </c>
       <c r="B20" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2442,21 +2442,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433474</v>
+        <v>432755</v>
       </c>
       <c r="R20" t="n">
-        <v>6765288</v>
+        <v>6764944</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2499,19 +2499,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2526,19 +2516,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130009995</v>
+        <v>130009997</v>
       </c>
       <c r="B21" t="n">
         <v>79180</v>
@@ -2573,10 +2563,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433498</v>
+        <v>433474</v>
       </c>
       <c r="R21" t="n">
-        <v>6765316</v>
+        <v>6765288</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2608,7 +2598,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2618,7 +2608,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2645,54 +2635,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130010428</v>
+        <v>130009995</v>
       </c>
       <c r="B22" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>432868</v>
+        <v>433498</v>
       </c>
       <c r="R22" t="n">
-        <v>6764991</v>
+        <v>6765316</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2722,75 +2703,93 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130010431</v>
+        <v>130010428</v>
       </c>
       <c r="B23" t="n">
-        <v>78937</v>
+        <v>8451</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>432755</v>
+        <v>432868</v>
       </c>
       <c r="R23" t="n">
-        <v>6764944</v>
+        <v>6764991</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2831,6 +2830,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -4843,10 +4843,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130000800</v>
+        <v>130009993</v>
       </c>
       <c r="B43" t="n">
-        <v>79181</v>
+        <v>79180</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4854,16 +4854,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4874,14 +4874,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>433464</v>
+        <v>433494</v>
       </c>
       <c r="R43" t="n">
-        <v>6765289</v>
+        <v>6765320</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4932,64 +4932,72 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130000806</v>
+        <v>130010429</v>
       </c>
       <c r="B44" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>432829</v>
+        <v>432898</v>
       </c>
       <c r="R44" t="n">
-        <v>6765145</v>
+        <v>6764968</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5019,93 +5027,75 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130010429</v>
+        <v>130000800</v>
       </c>
       <c r="B45" t="n">
-        <v>8451</v>
+        <v>79181</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>230405</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>432898</v>
+        <v>433464</v>
       </c>
       <c r="R45" t="n">
-        <v>6764968</v>
+        <v>6765289</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5135,9 +5125,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5153,19 +5153,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130009993</v>
+        <v>130000806</v>
       </c>
       <c r="B46" t="n">
         <v>79180</v>
@@ -5196,14 +5196,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>433494</v>
+        <v>432829</v>
       </c>
       <c r="R46" t="n">
-        <v>6765320</v>
+        <v>6765145</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5260,12 +5260,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>

--- a/artfynd/A 56940-2025 artfynd.xlsx
+++ b/artfynd/A 56940-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129998703</v>
+        <v>129998697</v>
       </c>
       <c r="B4" t="n">
-        <v>8451</v>
+        <v>78938</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432909</v>
+        <v>433506</v>
       </c>
       <c r="R4" t="n">
-        <v>6765182</v>
+        <v>6765247</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129998697</v>
+        <v>129998703</v>
       </c>
       <c r="B5" t="n">
-        <v>78938</v>
+        <v>8451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>433506</v>
+        <v>432909</v>
       </c>
       <c r="R5" t="n">
-        <v>6765247</v>
+        <v>6765182</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1744,10 +1744,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129998698</v>
+        <v>129998687</v>
       </c>
       <c r="B13" t="n">
-        <v>78938</v>
+        <v>79770</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1755,21 +1755,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432754</v>
+        <v>432898</v>
       </c>
       <c r="R13" t="n">
-        <v>6764932</v>
+        <v>6764900</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129998687</v>
+        <v>129998698</v>
       </c>
       <c r="B14" t="n">
-        <v>79770</v>
+        <v>78938</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1852,21 +1852,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432898</v>
+        <v>432754</v>
       </c>
       <c r="R14" t="n">
-        <v>6764900</v>
+        <v>6764932</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -4317,7 +4317,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130009980</v>
+        <v>130010425</v>
       </c>
       <c r="B38" t="n">
         <v>90760</v>
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>433320</v>
+        <v>432853</v>
       </c>
       <c r="R38" t="n">
-        <v>6765160</v>
+        <v>6765042</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4385,94 +4385,74 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130009982</v>
+        <v>130009980</v>
       </c>
       <c r="B39" t="n">
-        <v>8451</v>
+        <v>90760</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>1962</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>433497</v>
+        <v>433320</v>
       </c>
       <c r="R39" t="n">
-        <v>6765321</v>
+        <v>6765160</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4504,7 +4484,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4514,7 +4494,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4542,45 +4522,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130010425</v>
+        <v>130009982</v>
       </c>
       <c r="B40" t="n">
-        <v>90760</v>
+        <v>8451</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>432853</v>
+        <v>433497</v>
       </c>
       <c r="R40" t="n">
-        <v>6765042</v>
+        <v>6765321</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4610,36 +4599,47 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130009998</v>
+        <v>130010442</v>
       </c>
       <c r="B41" t="n">
         <v>79180</v>
@@ -4674,10 +4674,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>433400</v>
+        <v>432625</v>
       </c>
       <c r="R41" t="n">
-        <v>6765137</v>
+        <v>6764870</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4707,19 +4707,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4734,19 +4724,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130010442</v>
+        <v>130009998</v>
       </c>
       <c r="B42" t="n">
         <v>79180</v>
@@ -4781,10 +4771,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>432625</v>
+        <v>433400</v>
       </c>
       <c r="R42" t="n">
-        <v>6764870</v>
+        <v>6765137</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4814,9 +4804,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4831,12 +4831,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -8409,45 +8409,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130010435</v>
+        <v>130000798</v>
       </c>
       <c r="B77" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>433498</v>
+        <v>432873</v>
       </c>
       <c r="R77" t="n">
-        <v>6765212</v>
+        <v>6764999</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8477,9 +8477,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8494,57 +8504,57 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130000798</v>
+        <v>130010435</v>
       </c>
       <c r="B78" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>432873</v>
+        <v>433498</v>
       </c>
       <c r="R78" t="n">
-        <v>6764999</v>
+        <v>6765212</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8574,19 +8584,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8601,22 +8601,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130010445</v>
+        <v>130010003</v>
       </c>
       <c r="B79" t="n">
-        <v>78187</v>
+        <v>79180</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8624,21 +8624,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8648,10 +8648,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>433119</v>
+        <v>432841</v>
       </c>
       <c r="R79" t="n">
-        <v>6765204</v>
+        <v>6764949</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8681,9 +8681,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8698,22 +8708,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130010003</v>
+        <v>130010445</v>
       </c>
       <c r="B80" t="n">
-        <v>79180</v>
+        <v>78187</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8721,21 +8731,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8745,10 +8755,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>432841</v>
+        <v>433119</v>
       </c>
       <c r="R80" t="n">
-        <v>6764949</v>
+        <v>6765204</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8778,19 +8788,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>10:55</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8805,12 +8805,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>

--- a/artfynd/A 56940-2025 artfynd.xlsx
+++ b/artfynd/A 56940-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129998697</v>
+        <v>129998703</v>
       </c>
       <c r="B4" t="n">
-        <v>78938</v>
+        <v>8451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433506</v>
+        <v>432909</v>
       </c>
       <c r="R4" t="n">
-        <v>6765247</v>
+        <v>6765182</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129998703</v>
+        <v>129998697</v>
       </c>
       <c r="B5" t="n">
-        <v>8451</v>
+        <v>78938</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432909</v>
+        <v>433506</v>
       </c>
       <c r="R5" t="n">
-        <v>6765182</v>
+        <v>6765247</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129998706</v>
+        <v>129998718</v>
       </c>
       <c r="B8" t="n">
-        <v>8451</v>
+        <v>79181</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>230405</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>432738</v>
+        <v>433287</v>
       </c>
       <c r="R8" t="n">
-        <v>6764941</v>
+        <v>6765093</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1336,6 +1336,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1354,32 +1355,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129998718</v>
+        <v>129998706</v>
       </c>
       <c r="B9" t="n">
-        <v>79181</v>
+        <v>8451</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>230405</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1390,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433287</v>
+        <v>432738</v>
       </c>
       <c r="R9" t="n">
-        <v>6765093</v>
+        <v>6764941</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1433,7 +1434,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1452,32 +1452,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129998683</v>
+        <v>129998704</v>
       </c>
       <c r="B10" t="n">
-        <v>79770</v>
+        <v>8451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433347</v>
+        <v>432886</v>
       </c>
       <c r="R10" t="n">
-        <v>6765088</v>
+        <v>6765067</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1549,32 +1549,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129998704</v>
+        <v>129998683</v>
       </c>
       <c r="B11" t="n">
-        <v>8451</v>
+        <v>79770</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>432886</v>
+        <v>433347</v>
       </c>
       <c r="R11" t="n">
-        <v>6765067</v>
+        <v>6765088</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1744,10 +1744,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129998687</v>
+        <v>129998698</v>
       </c>
       <c r="B13" t="n">
-        <v>79770</v>
+        <v>78938</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1755,21 +1755,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432898</v>
+        <v>432754</v>
       </c>
       <c r="R13" t="n">
-        <v>6764900</v>
+        <v>6764932</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129998698</v>
+        <v>129998687</v>
       </c>
       <c r="B14" t="n">
-        <v>78938</v>
+        <v>79770</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1852,21 +1852,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432754</v>
+        <v>432898</v>
       </c>
       <c r="R14" t="n">
-        <v>6764932</v>
+        <v>6764900</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130010431</v>
+        <v>130009995</v>
       </c>
       <c r="B20" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2442,21 +2442,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>432755</v>
+        <v>433498</v>
       </c>
       <c r="R20" t="n">
-        <v>6764944</v>
+        <v>6765316</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2499,9 +2499,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2516,22 +2526,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130009997</v>
+        <v>130010431</v>
       </c>
       <c r="B21" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2539,21 +2549,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2563,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433474</v>
+        <v>432755</v>
       </c>
       <c r="R21" t="n">
-        <v>6765288</v>
+        <v>6764944</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2596,19 +2606,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2623,19 +2623,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130009995</v>
+        <v>130009997</v>
       </c>
       <c r="B22" t="n">
         <v>79180</v>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>433498</v>
+        <v>433474</v>
       </c>
       <c r="R22" t="n">
-        <v>6765316</v>
+        <v>6765288</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2849,45 +2849,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130000797</v>
+        <v>130010447</v>
       </c>
       <c r="B24" t="n">
-        <v>8451</v>
+        <v>78187</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6487</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>432910</v>
+        <v>432743</v>
       </c>
       <c r="R24" t="n">
-        <v>6764964</v>
+        <v>6764890</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2917,19 +2917,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2944,12 +2934,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3063,45 +3053,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130010447</v>
+        <v>130000797</v>
       </c>
       <c r="B26" t="n">
-        <v>78187</v>
+        <v>8451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6487</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>432743</v>
+        <v>432910</v>
       </c>
       <c r="R26" t="n">
-        <v>6764890</v>
+        <v>6764964</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3131,9 +3121,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3148,19 +3148,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130010002</v>
+        <v>130010439</v>
       </c>
       <c r="B27" t="n">
         <v>79180</v>
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>432842</v>
+        <v>432941</v>
       </c>
       <c r="R27" t="n">
-        <v>6764945</v>
+        <v>6764955</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3228,19 +3228,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3255,66 +3245,57 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130009984</v>
+        <v>130000803</v>
       </c>
       <c r="B28" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>432757</v>
+        <v>433436</v>
       </c>
       <c r="R28" t="n">
-        <v>6764953</v>
+        <v>6765320</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3346,7 +3327,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3356,7 +3337,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3365,64 +3346,72 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130009976</v>
+        <v>130009984</v>
       </c>
       <c r="B29" t="n">
-        <v>79770</v>
+        <v>8451</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>432806</v>
+        <v>432757</v>
       </c>
       <c r="R29" t="n">
-        <v>6764957</v>
+        <v>6764953</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3454,7 +3443,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3464,7 +3453,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3473,6 +3462,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3491,7 +3481,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130010439</v>
+        <v>130010002</v>
       </c>
       <c r="B30" t="n">
         <v>79180</v>
@@ -3526,10 +3516,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>432941</v>
+        <v>432842</v>
       </c>
       <c r="R30" t="n">
-        <v>6764955</v>
+        <v>6764945</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3559,9 +3549,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3576,22 +3576,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130000803</v>
+        <v>130009976</v>
       </c>
       <c r="B31" t="n">
-        <v>79180</v>
+        <v>79770</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3599,34 +3599,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433436</v>
+        <v>432806</v>
       </c>
       <c r="R31" t="n">
-        <v>6765320</v>
+        <v>6764957</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3683,22 +3683,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130010446</v>
+        <v>130010440</v>
       </c>
       <c r="B32" t="n">
-        <v>78187</v>
+        <v>79180</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3706,21 +3706,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3730,10 +3730,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>432787</v>
+        <v>432846</v>
       </c>
       <c r="R32" t="n">
-        <v>6764952</v>
+        <v>6764945</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3792,7 +3792,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130010440</v>
+        <v>130009999</v>
       </c>
       <c r="B33" t="n">
         <v>79180</v>
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>432846</v>
+        <v>433404</v>
       </c>
       <c r="R33" t="n">
-        <v>6764945</v>
+        <v>6765152</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3860,9 +3860,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3877,22 +3887,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130009999</v>
+        <v>130010446</v>
       </c>
       <c r="B34" t="n">
-        <v>79180</v>
+        <v>78187</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3900,21 +3910,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3924,10 +3934,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>433404</v>
+        <v>432787</v>
       </c>
       <c r="R34" t="n">
-        <v>6765152</v>
+        <v>6764952</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3957,19 +3967,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3984,22 +3984,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130000795</v>
+        <v>130009986</v>
       </c>
       <c r="B35" t="n">
-        <v>79770</v>
+        <v>78937</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4007,34 +4007,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>432795</v>
+        <v>432880</v>
       </c>
       <c r="R35" t="n">
-        <v>6764980</v>
+        <v>6764902</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4091,12 +4091,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4210,10 +4210,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130009986</v>
+        <v>130000795</v>
       </c>
       <c r="B37" t="n">
-        <v>78937</v>
+        <v>79770</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4221,34 +4221,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>432880</v>
+        <v>432795</v>
       </c>
       <c r="R37" t="n">
-        <v>6764902</v>
+        <v>6764980</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4305,19 +4305,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130010425</v>
+        <v>130009980</v>
       </c>
       <c r="B38" t="n">
         <v>90760</v>
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>432853</v>
+        <v>433320</v>
       </c>
       <c r="R38" t="n">
-        <v>6765042</v>
+        <v>6765160</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4385,36 +4385,47 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130009980</v>
+        <v>130010425</v>
       </c>
       <c r="B39" t="n">
         <v>90760</v>
@@ -4449,10 +4460,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>433320</v>
+        <v>432853</v>
       </c>
       <c r="R39" t="n">
-        <v>6765160</v>
+        <v>6765042</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4482,40 +4493,29 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4639,7 +4639,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130010442</v>
+        <v>130009998</v>
       </c>
       <c r="B41" t="n">
         <v>79180</v>
@@ -4674,10 +4674,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>432625</v>
+        <v>433400</v>
       </c>
       <c r="R41" t="n">
-        <v>6764870</v>
+        <v>6765137</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4707,9 +4707,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4724,19 +4734,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130009998</v>
+        <v>130010442</v>
       </c>
       <c r="B42" t="n">
         <v>79180</v>
@@ -4771,10 +4781,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>433400</v>
+        <v>432625</v>
       </c>
       <c r="R42" t="n">
-        <v>6765137</v>
+        <v>6764870</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4804,19 +4814,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4831,22 +4831,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130009993</v>
+        <v>130010424</v>
       </c>
       <c r="B43" t="n">
-        <v>79180</v>
+        <v>90760</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4854,21 +4854,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4878,10 +4878,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>433494</v>
+        <v>433000</v>
       </c>
       <c r="R43" t="n">
-        <v>6765320</v>
+        <v>6765168</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4911,19 +4911,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:58</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4938,22 +4928,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130010429</v>
+        <v>130010444</v>
       </c>
       <c r="B44" t="n">
-        <v>8451</v>
+        <v>93010</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4961,43 +4951,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>432898</v>
+        <v>433284</v>
       </c>
       <c r="R44" t="n">
-        <v>6764968</v>
+        <v>6765098</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5038,7 +5019,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5057,10 +5037,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130000800</v>
+        <v>130009993</v>
       </c>
       <c r="B45" t="n">
-        <v>79181</v>
+        <v>79180</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5068,16 +5048,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5088,14 +5068,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>433464</v>
+        <v>433494</v>
       </c>
       <c r="R45" t="n">
-        <v>6765289</v>
+        <v>6765320</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5127,7 +5107,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5137,7 +5117,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5146,19 +5126,18 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5272,45 +5251,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130010444</v>
+        <v>130000800</v>
       </c>
       <c r="B47" t="n">
-        <v>93010</v>
+        <v>79181</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>230405</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>433284</v>
+        <v>433464</v>
       </c>
       <c r="R47" t="n">
-        <v>6765098</v>
+        <v>6765289</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5340,74 +5319,94 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130010424</v>
+        <v>130010429</v>
       </c>
       <c r="B48" t="n">
-        <v>90760</v>
+        <v>8451</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>433000</v>
+        <v>432898</v>
       </c>
       <c r="R48" t="n">
-        <v>6765168</v>
+        <v>6764968</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5448,6 +5447,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5466,45 +5466,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130009994</v>
+        <v>130000808</v>
       </c>
       <c r="B49" t="n">
-        <v>79180</v>
+        <v>93010</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>433500</v>
+        <v>432783</v>
       </c>
       <c r="R49" t="n">
-        <v>6765331</v>
+        <v>6765102</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5536,7 +5540,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5546,7 +5550,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5555,25 +5559,26 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130010441</v>
+        <v>130009994</v>
       </c>
       <c r="B50" t="n">
         <v>79180</v>
@@ -5608,10 +5613,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>432847</v>
+        <v>433500</v>
       </c>
       <c r="R50" t="n">
-        <v>6764943</v>
+        <v>6765331</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5641,9 +5646,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5658,61 +5673,57 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130000808</v>
+        <v>130010441</v>
       </c>
       <c r="B51" t="n">
-        <v>93010</v>
+        <v>79180</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>432783</v>
+        <v>432847</v>
       </c>
       <c r="R51" t="n">
-        <v>6765102</v>
+        <v>6764943</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5742,40 +5753,29 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6115,10 +6115,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130010423</v>
+        <v>130010437</v>
       </c>
       <c r="B55" t="n">
-        <v>79770</v>
+        <v>79180</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6126,21 +6126,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6150,10 +6150,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>432753</v>
+        <v>433359</v>
       </c>
       <c r="R55" t="n">
-        <v>6765037</v>
+        <v>6765114</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6212,45 +6212,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130010427</v>
+        <v>130000802</v>
       </c>
       <c r="B56" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>433049</v>
+        <v>432785</v>
       </c>
       <c r="R56" t="n">
-        <v>6765172</v>
+        <v>6765104</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6280,9 +6280,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6297,44 +6307,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130010437</v>
+        <v>130010427</v>
       </c>
       <c r="B57" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6344,10 +6354,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>433359</v>
+        <v>433049</v>
       </c>
       <c r="R57" t="n">
-        <v>6765114</v>
+        <v>6765172</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6406,10 +6416,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130000802</v>
+        <v>130010423</v>
       </c>
       <c r="B58" t="n">
-        <v>79180</v>
+        <v>79770</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6417,34 +6427,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>432785</v>
+        <v>432753</v>
       </c>
       <c r="R58" t="n">
-        <v>6765104</v>
+        <v>6765037</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6474,19 +6484,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>14:54</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6501,19 +6501,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130009989</v>
+        <v>130009991</v>
       </c>
       <c r="B59" t="n">
         <v>79180</v>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>433473</v>
+        <v>433469</v>
       </c>
       <c r="R59" t="n">
-        <v>6765313</v>
+        <v>6765340</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6620,54 +6620,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130009981</v>
+        <v>130010000</v>
       </c>
       <c r="B60" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>433429</v>
+        <v>432861</v>
       </c>
       <c r="R60" t="n">
-        <v>6765324</v>
+        <v>6764984</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6699,7 +6690,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6709,7 +6700,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6718,7 +6709,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6737,7 +6727,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130009991</v>
+        <v>130009989</v>
       </c>
       <c r="B61" t="n">
         <v>79180</v>
@@ -6772,10 +6762,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>433469</v>
+        <v>433473</v>
       </c>
       <c r="R61" t="n">
-        <v>6765340</v>
+        <v>6765313</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6807,7 +6797,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6817,7 +6807,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6844,7 +6834,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130010000</v>
+        <v>130010436</v>
       </c>
       <c r="B62" t="n">
         <v>79180</v>
@@ -6879,10 +6869,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>432861</v>
+        <v>433362</v>
       </c>
       <c r="R62" t="n">
-        <v>6764984</v>
+        <v>6765100</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6912,19 +6902,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>11:44</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6939,57 +6919,66 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130010436</v>
+        <v>130009981</v>
       </c>
       <c r="B63" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>433362</v>
+        <v>433429</v>
       </c>
       <c r="R63" t="n">
-        <v>6765100</v>
+        <v>6765324</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7019,74 +7008,94 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130009979</v>
+        <v>130010426</v>
       </c>
       <c r="B64" t="n">
-        <v>91749</v>
+        <v>8451</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>433285</v>
+        <v>433443</v>
       </c>
       <c r="R64" t="n">
-        <v>6765090</v>
+        <v>6765297</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7116,39 +7125,30 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7262,10 +7262,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130010434</v>
+        <v>130009979</v>
       </c>
       <c r="B66" t="n">
-        <v>79180</v>
+        <v>91749</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7273,21 +7273,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7297,10 +7297,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>433459</v>
+        <v>433285</v>
       </c>
       <c r="R66" t="n">
-        <v>6765287</v>
+        <v>6765090</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7330,9 +7330,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7347,66 +7357,57 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130010426</v>
+        <v>130010434</v>
       </c>
       <c r="B67" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>433443</v>
+        <v>433459</v>
       </c>
       <c r="R67" t="n">
-        <v>6765297</v>
+        <v>6765287</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7447,7 +7448,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7466,7 +7466,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130009992</v>
+        <v>130010432</v>
       </c>
       <c r="B68" t="n">
         <v>79180</v>
@@ -7501,10 +7501,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>433482</v>
+        <v>432782</v>
       </c>
       <c r="R68" t="n">
-        <v>6765315</v>
+        <v>6765113</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7534,19 +7534,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>13:59</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7561,19 +7551,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130009996</v>
+        <v>130009992</v>
       </c>
       <c r="B69" t="n">
         <v>79180</v>
@@ -7608,7 +7598,7 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>433488</v>
+        <v>433482</v>
       </c>
       <c r="R69" t="n">
         <v>6765315</v>
@@ -7643,7 +7633,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7653,7 +7643,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7680,7 +7670,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130010001</v>
+        <v>130009996</v>
       </c>
       <c r="B70" t="n">
         <v>79180</v>
@@ -7715,10 +7705,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>432965</v>
+        <v>433488</v>
       </c>
       <c r="R70" t="n">
-        <v>6764935</v>
+        <v>6765315</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7750,7 +7740,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7760,7 +7750,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7787,7 +7777,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130010432</v>
+        <v>130010001</v>
       </c>
       <c r="B71" t="n">
         <v>79180</v>
@@ -7822,10 +7812,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>432782</v>
+        <v>432965</v>
       </c>
       <c r="R71" t="n">
-        <v>6765113</v>
+        <v>6764935</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7855,9 +7845,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7872,57 +7872,57 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130000796</v>
+        <v>130010005</v>
       </c>
       <c r="B72" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>433217</v>
+        <v>432732</v>
       </c>
       <c r="R72" t="n">
-        <v>6765206</v>
+        <v>6764932</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7979,19 +7979,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130010005</v>
+        <v>130010433</v>
       </c>
       <c r="B73" t="n">
         <v>79180</v>
@@ -8026,10 +8026,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432732</v>
+        <v>432809</v>
       </c>
       <c r="R73" t="n">
-        <v>6764932</v>
+        <v>6765129</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8059,19 +8059,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>10:35</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8086,57 +8076,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130010433</v>
+        <v>130000796</v>
       </c>
       <c r="B74" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>432809</v>
+        <v>433217</v>
       </c>
       <c r="R74" t="n">
-        <v>6765129</v>
+        <v>6765206</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8166,9 +8156,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8183,57 +8183,57 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130009990</v>
+        <v>130000798</v>
       </c>
       <c r="B75" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>433472</v>
+        <v>432873</v>
       </c>
       <c r="R75" t="n">
-        <v>6765327</v>
+        <v>6764999</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8290,12 +8290,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8409,45 +8409,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130000798</v>
+        <v>130009990</v>
       </c>
       <c r="B77" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>432873</v>
+        <v>433472</v>
       </c>
       <c r="R77" t="n">
-        <v>6764999</v>
+        <v>6765327</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8504,12 +8504,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>

--- a/artfynd/A 56940-2025 artfynd.xlsx
+++ b/artfynd/A 56940-2025 artfynd.xlsx
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129998718</v>
+        <v>129998706</v>
       </c>
       <c r="B8" t="n">
-        <v>79181</v>
+        <v>8451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>230405</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>433287</v>
+        <v>432738</v>
       </c>
       <c r="R8" t="n">
-        <v>6765093</v>
+        <v>6764941</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1336,7 +1336,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1355,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129998706</v>
+        <v>129998718</v>
       </c>
       <c r="B9" t="n">
-        <v>8451</v>
+        <v>79181</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>230405</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1390,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>432738</v>
+        <v>433287</v>
       </c>
       <c r="R9" t="n">
-        <v>6764941</v>
+        <v>6765093</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1434,6 +1433,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1452,32 +1452,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129998704</v>
+        <v>129998683</v>
       </c>
       <c r="B10" t="n">
-        <v>8451</v>
+        <v>79770</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>432886</v>
+        <v>433347</v>
       </c>
       <c r="R10" t="n">
-        <v>6765067</v>
+        <v>6765088</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1549,10 +1549,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129998683</v>
+        <v>129998717</v>
       </c>
       <c r="B11" t="n">
-        <v>79770</v>
+        <v>79181</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1560,21 +1560,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>230405</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433347</v>
+        <v>433514</v>
       </c>
       <c r="R11" t="n">
-        <v>6765088</v>
+        <v>6765225</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1628,6 +1628,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1646,32 +1647,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129998717</v>
+        <v>129998704</v>
       </c>
       <c r="B12" t="n">
-        <v>79181</v>
+        <v>8451</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>230405</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1681,10 +1682,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433514</v>
+        <v>432886</v>
       </c>
       <c r="R12" t="n">
-        <v>6765225</v>
+        <v>6765067</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1725,7 +1726,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1744,10 +1744,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129998698</v>
+        <v>129998687</v>
       </c>
       <c r="B13" t="n">
-        <v>78938</v>
+        <v>79770</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1755,21 +1755,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432754</v>
+        <v>432898</v>
       </c>
       <c r="R13" t="n">
-        <v>6764932</v>
+        <v>6764900</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129998687</v>
+        <v>129998698</v>
       </c>
       <c r="B14" t="n">
-        <v>79770</v>
+        <v>78938</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1852,21 +1852,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432898</v>
+        <v>432754</v>
       </c>
       <c r="R14" t="n">
-        <v>6764900</v>
+        <v>6764932</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130009995</v>
+        <v>130010431</v>
       </c>
       <c r="B20" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2442,21 +2442,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433498</v>
+        <v>432755</v>
       </c>
       <c r="R20" t="n">
-        <v>6765316</v>
+        <v>6764944</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2499,19 +2499,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2526,22 +2516,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130010431</v>
+        <v>130009997</v>
       </c>
       <c r="B21" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2549,21 +2539,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2573,10 +2563,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>432755</v>
+        <v>433474</v>
       </c>
       <c r="R21" t="n">
-        <v>6764944</v>
+        <v>6765288</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2606,9 +2596,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2623,19 +2623,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130009997</v>
+        <v>130009995</v>
       </c>
       <c r="B22" t="n">
         <v>79180</v>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>433474</v>
+        <v>433498</v>
       </c>
       <c r="R22" t="n">
-        <v>6765288</v>
+        <v>6765316</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2946,32 +2946,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130000805</v>
+        <v>130000797</v>
       </c>
       <c r="B25" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>432810</v>
+        <v>432910</v>
       </c>
       <c r="R25" t="n">
-        <v>6765134</v>
+        <v>6764964</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3053,32 +3053,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130000797</v>
+        <v>130000805</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>432910</v>
+        <v>432810</v>
       </c>
       <c r="R26" t="n">
-        <v>6764964</v>
+        <v>6765134</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3160,45 +3160,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130010439</v>
+        <v>130009984</v>
       </c>
       <c r="B27" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>432941</v>
+        <v>432757</v>
       </c>
       <c r="R27" t="n">
-        <v>6764955</v>
+        <v>6764953</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3228,39 +3237,50 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130000803</v>
+        <v>130009976</v>
       </c>
       <c r="B28" t="n">
-        <v>79180</v>
+        <v>79770</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3268,34 +3288,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>433436</v>
+        <v>432806</v>
       </c>
       <c r="R28" t="n">
-        <v>6765320</v>
+        <v>6764957</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3327,7 +3347,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3337,7 +3357,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3352,66 +3372,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130009984</v>
+        <v>130010439</v>
       </c>
       <c r="B29" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>432757</v>
+        <v>432941</v>
       </c>
       <c r="R29" t="n">
-        <v>6764953</v>
+        <v>6764955</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3441,40 +3452,29 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130009976</v>
+        <v>130000803</v>
       </c>
       <c r="B31" t="n">
-        <v>79770</v>
+        <v>79180</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3599,34 +3599,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>432806</v>
+        <v>433436</v>
       </c>
       <c r="R31" t="n">
-        <v>6764957</v>
+        <v>6765320</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3683,19 +3683,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130010440</v>
+        <v>130009999</v>
       </c>
       <c r="B32" t="n">
         <v>79180</v>
@@ -3730,10 +3730,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>432846</v>
+        <v>433404</v>
       </c>
       <c r="R32" t="n">
-        <v>6764945</v>
+        <v>6765152</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3763,9 +3763,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3780,22 +3790,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130009999</v>
+        <v>130010446</v>
       </c>
       <c r="B33" t="n">
-        <v>79180</v>
+        <v>78187</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3803,21 +3813,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3827,10 +3837,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>433404</v>
+        <v>432787</v>
       </c>
       <c r="R33" t="n">
-        <v>6765152</v>
+        <v>6764952</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3860,19 +3870,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3887,22 +3887,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130010446</v>
+        <v>130010440</v>
       </c>
       <c r="B34" t="n">
-        <v>78187</v>
+        <v>79180</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3910,21 +3910,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>432787</v>
+        <v>432846</v>
       </c>
       <c r="R34" t="n">
-        <v>6764952</v>
+        <v>6764945</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4317,45 +4317,54 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130009980</v>
+        <v>130009982</v>
       </c>
       <c r="B38" t="n">
-        <v>90760</v>
+        <v>8451</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>433320</v>
+        <v>433497</v>
       </c>
       <c r="R38" t="n">
-        <v>6765160</v>
+        <v>6765321</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4387,7 +4396,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4397,7 +4406,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4425,7 +4434,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130010425</v>
+        <v>130009980</v>
       </c>
       <c r="B39" t="n">
         <v>90760</v>
@@ -4460,10 +4469,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>432853</v>
+        <v>433320</v>
       </c>
       <c r="R39" t="n">
-        <v>6765042</v>
+        <v>6765160</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4493,83 +4502,85 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130009982</v>
+        <v>130010425</v>
       </c>
       <c r="B40" t="n">
-        <v>8451</v>
+        <v>90760</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>1962</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>433497</v>
+        <v>432853</v>
       </c>
       <c r="R40" t="n">
-        <v>6765321</v>
+        <v>6765042</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4599,40 +4610,29 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5037,7 +5037,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130009993</v>
+        <v>130000806</v>
       </c>
       <c r="B45" t="n">
         <v>79180</v>
@@ -5068,14 +5068,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>433494</v>
+        <v>432829</v>
       </c>
       <c r="R45" t="n">
-        <v>6765320</v>
+        <v>6765145</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5132,19 +5132,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130000806</v>
+        <v>130009993</v>
       </c>
       <c r="B46" t="n">
         <v>79180</v>
@@ -5175,14 +5175,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>432829</v>
+        <v>433494</v>
       </c>
       <c r="R46" t="n">
-        <v>6765145</v>
+        <v>6765320</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5239,57 +5239,66 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130000800</v>
+        <v>130010429</v>
       </c>
       <c r="B47" t="n">
-        <v>79181</v>
+        <v>8451</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>230405</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>433464</v>
+        <v>432898</v>
       </c>
       <c r="R47" t="n">
-        <v>6765289</v>
+        <v>6764968</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5319,19 +5328,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>13:57</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5347,66 +5346,57 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130010429</v>
+        <v>130000800</v>
       </c>
       <c r="B48" t="n">
-        <v>8451</v>
+        <v>79181</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>230405</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>432898</v>
+        <v>433464</v>
       </c>
       <c r="R48" t="n">
-        <v>6764968</v>
+        <v>6765289</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5436,9 +5426,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5454,61 +5454,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130000808</v>
+        <v>130010441</v>
       </c>
       <c r="B49" t="n">
-        <v>93010</v>
+        <v>79180</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>432783</v>
+        <v>432847</v>
       </c>
       <c r="R49" t="n">
-        <v>6765102</v>
+        <v>6764943</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5538,85 +5534,78 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130009994</v>
+        <v>130000808</v>
       </c>
       <c r="B50" t="n">
-        <v>79180</v>
+        <v>93010</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>433500</v>
+        <v>432783</v>
       </c>
       <c r="R50" t="n">
-        <v>6765331</v>
+        <v>6765102</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5648,7 +5637,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5658,7 +5647,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5667,25 +5656,26 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130010441</v>
+        <v>130009994</v>
       </c>
       <c r="B51" t="n">
         <v>79180</v>
@@ -5720,10 +5710,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>432847</v>
+        <v>433500</v>
       </c>
       <c r="R51" t="n">
-        <v>6764943</v>
+        <v>6765331</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5753,9 +5743,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5770,12 +5770,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5879,45 +5879,43 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130009978</v>
+        <v>130009983</v>
       </c>
       <c r="B53" t="n">
-        <v>91749</v>
+        <v>8451</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -5925,10 +5923,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>433075</v>
+        <v>432870</v>
       </c>
       <c r="R53" t="n">
-        <v>6765186</v>
+        <v>6764928</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5960,7 +5958,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -5970,7 +5968,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5998,43 +5996,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130009983</v>
+        <v>130009978</v>
       </c>
       <c r="B54" t="n">
-        <v>8451</v>
+        <v>91749</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>432870</v>
+        <v>433075</v>
       </c>
       <c r="R54" t="n">
-        <v>6764928</v>
+        <v>6765186</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6513,7 +6513,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130009991</v>
+        <v>130010436</v>
       </c>
       <c r="B59" t="n">
         <v>79180</v>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>433469</v>
+        <v>433362</v>
       </c>
       <c r="R59" t="n">
-        <v>6765340</v>
+        <v>6765100</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6581,19 +6581,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>13:59</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6608,19 +6598,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130010000</v>
+        <v>130009989</v>
       </c>
       <c r="B60" t="n">
         <v>79180</v>
@@ -6655,10 +6645,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>432861</v>
+        <v>433473</v>
       </c>
       <c r="R60" t="n">
-        <v>6764984</v>
+        <v>6765313</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6690,7 +6680,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6700,7 +6690,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6727,7 +6717,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130009989</v>
+        <v>130009991</v>
       </c>
       <c r="B61" t="n">
         <v>79180</v>
@@ -6762,10 +6752,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>433473</v>
+        <v>433469</v>
       </c>
       <c r="R61" t="n">
-        <v>6765313</v>
+        <v>6765340</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6797,7 +6787,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6807,7 +6797,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6834,7 +6824,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130010436</v>
+        <v>130010000</v>
       </c>
       <c r="B62" t="n">
         <v>79180</v>
@@ -6869,10 +6859,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>433362</v>
+        <v>432861</v>
       </c>
       <c r="R62" t="n">
-        <v>6765100</v>
+        <v>6764984</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6902,9 +6892,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6919,12 +6919,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7048,54 +7048,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130010426</v>
+        <v>130009979</v>
       </c>
       <c r="B64" t="n">
-        <v>8451</v>
+        <v>91749</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>433443</v>
+        <v>433285</v>
       </c>
       <c r="R64" t="n">
-        <v>6765297</v>
+        <v>6765090</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7125,37 +7116,46 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130010004</v>
+        <v>130010434</v>
       </c>
       <c r="B65" t="n">
         <v>79180</v>
@@ -7190,10 +7190,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432836</v>
+        <v>433459</v>
       </c>
       <c r="R65" t="n">
-        <v>6764947</v>
+        <v>6765287</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7223,19 +7223,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>10:53</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7250,57 +7240,66 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130009979</v>
+        <v>130010426</v>
       </c>
       <c r="B66" t="n">
-        <v>91749</v>
+        <v>8451</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>433285</v>
+        <v>433443</v>
       </c>
       <c r="R66" t="n">
-        <v>6765090</v>
+        <v>6765297</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7330,46 +7329,37 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130010434</v>
+        <v>130010004</v>
       </c>
       <c r="B67" t="n">
         <v>79180</v>
@@ -7404,10 +7394,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>433459</v>
+        <v>432836</v>
       </c>
       <c r="R67" t="n">
-        <v>6765287</v>
+        <v>6764947</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7437,9 +7427,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7454,12 +7454,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7563,7 +7563,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130009992</v>
+        <v>130009996</v>
       </c>
       <c r="B69" t="n">
         <v>79180</v>
@@ -7598,7 +7598,7 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>433482</v>
+        <v>433488</v>
       </c>
       <c r="R69" t="n">
         <v>6765315</v>
@@ -7633,7 +7633,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7670,7 +7670,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130009996</v>
+        <v>130009992</v>
       </c>
       <c r="B70" t="n">
         <v>79180</v>
@@ -7705,7 +7705,7 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>433488</v>
+        <v>433482</v>
       </c>
       <c r="R70" t="n">
         <v>6765315</v>
@@ -7740,7 +7740,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7884,7 +7884,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130010005</v>
+        <v>130010433</v>
       </c>
       <c r="B72" t="n">
         <v>79180</v>
@@ -7919,10 +7919,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>432732</v>
+        <v>432809</v>
       </c>
       <c r="R72" t="n">
-        <v>6764932</v>
+        <v>6765129</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7952,19 +7952,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>10:35</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7979,19 +7969,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130010433</v>
+        <v>130010005</v>
       </c>
       <c r="B73" t="n">
         <v>79180</v>
@@ -8026,10 +8016,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432809</v>
+        <v>432732</v>
       </c>
       <c r="R73" t="n">
-        <v>6765129</v>
+        <v>6764932</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8059,9 +8049,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8076,12 +8076,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8302,7 +8302,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130009988</v>
+        <v>130010435</v>
       </c>
       <c r="B76" t="n">
         <v>79180</v>
@@ -8337,10 +8337,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>433439</v>
+        <v>433498</v>
       </c>
       <c r="R76" t="n">
-        <v>6765313</v>
+        <v>6765212</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8370,19 +8370,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>14:09</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8397,19 +8387,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130009990</v>
+        <v>130009988</v>
       </c>
       <c r="B77" t="n">
         <v>79180</v>
@@ -8444,10 +8434,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>433472</v>
+        <v>433439</v>
       </c>
       <c r="R77" t="n">
-        <v>6765327</v>
+        <v>6765313</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8479,7 +8469,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8489,7 +8479,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8516,7 +8506,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130010435</v>
+        <v>130009990</v>
       </c>
       <c r="B78" t="n">
         <v>79180</v>
@@ -8551,10 +8541,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>433498</v>
+        <v>433472</v>
       </c>
       <c r="R78" t="n">
-        <v>6765212</v>
+        <v>6765327</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8584,9 +8574,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8601,12 +8601,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 56940-2025 artfynd.xlsx
+++ b/artfynd/A 56940-2025 artfynd.xlsx
@@ -1452,32 +1452,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129998683</v>
+        <v>129998704</v>
       </c>
       <c r="B10" t="n">
-        <v>79770</v>
+        <v>8451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433347</v>
+        <v>432886</v>
       </c>
       <c r="R10" t="n">
-        <v>6765088</v>
+        <v>6765067</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1549,10 +1549,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129998717</v>
+        <v>129998683</v>
       </c>
       <c r="B11" t="n">
-        <v>79181</v>
+        <v>79770</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1560,21 +1560,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>230405</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433514</v>
+        <v>433347</v>
       </c>
       <c r="R11" t="n">
-        <v>6765225</v>
+        <v>6765088</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1628,7 +1628,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1647,32 +1646,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129998704</v>
+        <v>129998717</v>
       </c>
       <c r="B12" t="n">
-        <v>8451</v>
+        <v>79181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>230405</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1682,10 +1681,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432886</v>
+        <v>433514</v>
       </c>
       <c r="R12" t="n">
-        <v>6765067</v>
+        <v>6765225</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1726,6 +1725,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1744,10 +1744,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129998687</v>
+        <v>129998698</v>
       </c>
       <c r="B13" t="n">
-        <v>79770</v>
+        <v>78938</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1755,21 +1755,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432898</v>
+        <v>432754</v>
       </c>
       <c r="R13" t="n">
-        <v>6764900</v>
+        <v>6764932</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129998698</v>
+        <v>129998687</v>
       </c>
       <c r="B14" t="n">
-        <v>78938</v>
+        <v>79770</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1852,21 +1852,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432754</v>
+        <v>432898</v>
       </c>
       <c r="R14" t="n">
-        <v>6764932</v>
+        <v>6764900</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2133,32 +2133,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129998701</v>
+        <v>129998690</v>
       </c>
       <c r="B17" t="n">
-        <v>8451</v>
+        <v>91749</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433145</v>
+        <v>433075</v>
       </c>
       <c r="R17" t="n">
-        <v>6765198</v>
+        <v>6765183</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2206,13 +2206,17 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1 st. Inte samma träd som tickorna bredvid.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2329,32 +2333,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129998690</v>
+        <v>129998701</v>
       </c>
       <c r="B19" t="n">
-        <v>91749</v>
+        <v>8451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433075</v>
+        <v>433145</v>
       </c>
       <c r="R19" t="n">
-        <v>6765183</v>
+        <v>6765198</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2402,17 +2406,13 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>1 st. Inte samma träd som tickorna bredvid.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2431,45 +2431,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130010431</v>
+        <v>130010428</v>
       </c>
       <c r="B20" t="n">
-        <v>78937</v>
+        <v>8451</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>432755</v>
+        <v>432868</v>
       </c>
       <c r="R20" t="n">
-        <v>6764944</v>
+        <v>6764991</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2510,6 +2519,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2742,54 +2752,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130010428</v>
+        <v>130010431</v>
       </c>
       <c r="B23" t="n">
-        <v>8451</v>
+        <v>78937</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>432868</v>
+        <v>432755</v>
       </c>
       <c r="R23" t="n">
-        <v>6764991</v>
+        <v>6764944</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2830,7 +2831,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2849,45 +2849,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130010447</v>
+        <v>130000797</v>
       </c>
       <c r="B24" t="n">
-        <v>78187</v>
+        <v>8451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6487</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>432743</v>
+        <v>432910</v>
       </c>
       <c r="R24" t="n">
-        <v>6764890</v>
+        <v>6764964</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2917,9 +2917,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2934,57 +2944,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130000797</v>
+        <v>130010447</v>
       </c>
       <c r="B25" t="n">
-        <v>8451</v>
+        <v>78187</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6487</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>432910</v>
+        <v>432743</v>
       </c>
       <c r="R25" t="n">
-        <v>6764964</v>
+        <v>6764890</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3014,19 +3024,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3041,12 +3041,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3160,54 +3160,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130009984</v>
+        <v>130010439</v>
       </c>
       <c r="B27" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>432757</v>
+        <v>432941</v>
       </c>
       <c r="R27" t="n">
-        <v>6764953</v>
+        <v>6764955</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3237,50 +3228,39 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130009976</v>
+        <v>130010002</v>
       </c>
       <c r="B28" t="n">
-        <v>79770</v>
+        <v>79180</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3288,21 +3268,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3312,10 +3292,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>432806</v>
+        <v>432842</v>
       </c>
       <c r="R28" t="n">
-        <v>6764957</v>
+        <v>6764945</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3347,7 +3327,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3357,7 +3337,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3384,7 +3364,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130010439</v>
+        <v>130000803</v>
       </c>
       <c r="B29" t="n">
         <v>79180</v>
@@ -3415,14 +3395,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>432941</v>
+        <v>433436</v>
       </c>
       <c r="R29" t="n">
-        <v>6764955</v>
+        <v>6765320</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3452,9 +3432,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3469,57 +3459,66 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130010002</v>
+        <v>130009984</v>
       </c>
       <c r="B30" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>432842</v>
+        <v>432757</v>
       </c>
       <c r="R30" t="n">
-        <v>6764945</v>
+        <v>6764953</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3551,7 +3550,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3561,7 +3560,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3570,6 +3569,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3588,10 +3588,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130000803</v>
+        <v>130009976</v>
       </c>
       <c r="B31" t="n">
-        <v>79180</v>
+        <v>79770</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3599,34 +3599,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433436</v>
+        <v>432806</v>
       </c>
       <c r="R31" t="n">
-        <v>6765320</v>
+        <v>6764957</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3683,12 +3683,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3802,10 +3802,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130010446</v>
+        <v>130010440</v>
       </c>
       <c r="B33" t="n">
-        <v>78187</v>
+        <v>79180</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3813,21 +3813,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>432787</v>
+        <v>432846</v>
       </c>
       <c r="R33" t="n">
-        <v>6764952</v>
+        <v>6764945</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3899,10 +3899,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130010440</v>
+        <v>130010446</v>
       </c>
       <c r="B34" t="n">
-        <v>79180</v>
+        <v>78187</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3910,21 +3910,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>432846</v>
+        <v>432787</v>
       </c>
       <c r="R34" t="n">
-        <v>6764945</v>
+        <v>6764952</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4103,7 +4103,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130009975</v>
+        <v>130000795</v>
       </c>
       <c r="B36" t="n">
         <v>79770</v>
@@ -4134,14 +4134,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>432801</v>
+        <v>432795</v>
       </c>
       <c r="R36" t="n">
-        <v>6765083</v>
+        <v>6764980</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4198,19 +4198,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130000795</v>
+        <v>130009975</v>
       </c>
       <c r="B37" t="n">
         <v>79770</v>
@@ -4241,14 +4241,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>432795</v>
+        <v>432801</v>
       </c>
       <c r="R37" t="n">
-        <v>6764980</v>
+        <v>6765083</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4305,66 +4305,57 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130009982</v>
+        <v>130009980</v>
       </c>
       <c r="B38" t="n">
-        <v>8451</v>
+        <v>90760</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>1962</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>433497</v>
+        <v>433320</v>
       </c>
       <c r="R38" t="n">
-        <v>6765321</v>
+        <v>6765160</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4396,7 +4387,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4406,7 +4397,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4434,7 +4425,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130009980</v>
+        <v>130010425</v>
       </c>
       <c r="B39" t="n">
         <v>90760</v>
@@ -4469,10 +4460,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>433320</v>
+        <v>432853</v>
       </c>
       <c r="R39" t="n">
-        <v>6765160</v>
+        <v>6765042</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4502,85 +4493,83 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130010425</v>
+        <v>130009982</v>
       </c>
       <c r="B40" t="n">
-        <v>90760</v>
+        <v>8451</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>432853</v>
+        <v>433497</v>
       </c>
       <c r="R40" t="n">
-        <v>6765042</v>
+        <v>6765321</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4610,29 +4599,40 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4843,32 +4843,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130010424</v>
+        <v>130010444</v>
       </c>
       <c r="B43" t="n">
-        <v>90760</v>
+        <v>93010</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4878,10 +4878,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>433000</v>
+        <v>433284</v>
       </c>
       <c r="R43" t="n">
-        <v>6765168</v>
+        <v>6765098</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4940,32 +4940,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130010444</v>
+        <v>130010424</v>
       </c>
       <c r="B44" t="n">
-        <v>93010</v>
+        <v>90760</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4975,10 +4975,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>433284</v>
+        <v>433000</v>
       </c>
       <c r="R44" t="n">
-        <v>6765098</v>
+        <v>6765168</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5466,45 +5466,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130010441</v>
+        <v>130000808</v>
       </c>
       <c r="B49" t="n">
-        <v>79180</v>
+        <v>93010</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>432847</v>
+        <v>432783</v>
       </c>
       <c r="R49" t="n">
-        <v>6764943</v>
+        <v>6765102</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5534,78 +5538,85 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130000808</v>
+        <v>130009994</v>
       </c>
       <c r="B50" t="n">
-        <v>93010</v>
+        <v>79180</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>432783</v>
+        <v>433500</v>
       </c>
       <c r="R50" t="n">
-        <v>6765102</v>
+        <v>6765331</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5637,7 +5648,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5647,7 +5658,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5656,26 +5667,25 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130009994</v>
+        <v>130010441</v>
       </c>
       <c r="B51" t="n">
         <v>79180</v>
@@ -5710,10 +5720,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>433500</v>
+        <v>432847</v>
       </c>
       <c r="R51" t="n">
-        <v>6765331</v>
+        <v>6764943</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5743,19 +5753,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>13:57</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5770,12 +5770,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5879,43 +5879,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130009983</v>
+        <v>130009978</v>
       </c>
       <c r="B53" t="n">
-        <v>8451</v>
+        <v>91749</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -5923,10 +5925,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>432870</v>
+        <v>433075</v>
       </c>
       <c r="R53" t="n">
-        <v>6764928</v>
+        <v>6765186</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5958,7 +5960,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -5968,7 +5970,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5996,45 +5998,43 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130009978</v>
+        <v>130009983</v>
       </c>
       <c r="B54" t="n">
-        <v>91749</v>
+        <v>8451</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>433075</v>
+        <v>432870</v>
       </c>
       <c r="R54" t="n">
-        <v>6765186</v>
+        <v>6764928</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6115,32 +6115,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130010437</v>
+        <v>130010427</v>
       </c>
       <c r="B55" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6150,10 +6150,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>433359</v>
+        <v>433049</v>
       </c>
       <c r="R55" t="n">
-        <v>6765114</v>
+        <v>6765172</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6212,10 +6212,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130000802</v>
+        <v>130010423</v>
       </c>
       <c r="B56" t="n">
-        <v>79180</v>
+        <v>79770</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6223,34 +6223,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>432785</v>
+        <v>432753</v>
       </c>
       <c r="R56" t="n">
-        <v>6765104</v>
+        <v>6765037</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6280,19 +6280,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>14:54</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6307,44 +6297,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130010427</v>
+        <v>130010437</v>
       </c>
       <c r="B57" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6354,10 +6344,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>433049</v>
+        <v>433359</v>
       </c>
       <c r="R57" t="n">
-        <v>6765172</v>
+        <v>6765114</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6416,10 +6406,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130010423</v>
+        <v>130000802</v>
       </c>
       <c r="B58" t="n">
-        <v>79770</v>
+        <v>79180</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6427,34 +6417,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>432753</v>
+        <v>432785</v>
       </c>
       <c r="R58" t="n">
-        <v>6765037</v>
+        <v>6765104</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6484,9 +6474,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6501,57 +6501,66 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130010436</v>
+        <v>130009981</v>
       </c>
       <c r="B59" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>433362</v>
+        <v>433429</v>
       </c>
       <c r="R59" t="n">
-        <v>6765100</v>
+        <v>6765324</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6581,36 +6590,47 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130009989</v>
+        <v>130010436</v>
       </c>
       <c r="B60" t="n">
         <v>79180</v>
@@ -6645,10 +6665,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>433473</v>
+        <v>433362</v>
       </c>
       <c r="R60" t="n">
-        <v>6765313</v>
+        <v>6765100</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6678,19 +6698,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6705,19 +6715,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130009991</v>
+        <v>130009989</v>
       </c>
       <c r="B61" t="n">
         <v>79180</v>
@@ -6752,10 +6762,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>433469</v>
+        <v>433473</v>
       </c>
       <c r="R61" t="n">
-        <v>6765340</v>
+        <v>6765313</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6787,7 +6797,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6797,7 +6807,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6824,7 +6834,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130010000</v>
+        <v>130009991</v>
       </c>
       <c r="B62" t="n">
         <v>79180</v>
@@ -6859,10 +6869,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>432861</v>
+        <v>433469</v>
       </c>
       <c r="R62" t="n">
-        <v>6764984</v>
+        <v>6765340</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6894,7 +6904,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -6904,7 +6914,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6931,54 +6941,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130009981</v>
+        <v>130010000</v>
       </c>
       <c r="B63" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>433429</v>
+        <v>432861</v>
       </c>
       <c r="R63" t="n">
-        <v>6765324</v>
+        <v>6764984</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7010,7 +7011,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7020,7 +7021,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7029,7 +7030,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7252,54 +7252,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130010426</v>
+        <v>130010004</v>
       </c>
       <c r="B66" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>433443</v>
+        <v>432836</v>
       </c>
       <c r="R66" t="n">
-        <v>6765297</v>
+        <v>6764947</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7329,75 +7320,93 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130010004</v>
+        <v>130010426</v>
       </c>
       <c r="B67" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>432836</v>
+        <v>433443</v>
       </c>
       <c r="R67" t="n">
-        <v>6764947</v>
+        <v>6765297</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7427,46 +7436,37 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130010432</v>
+        <v>130009992</v>
       </c>
       <c r="B68" t="n">
         <v>79180</v>
@@ -7501,10 +7501,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>432782</v>
+        <v>433482</v>
       </c>
       <c r="R68" t="n">
-        <v>6765113</v>
+        <v>6765315</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7534,9 +7534,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7551,12 +7561,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7670,7 +7680,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130009992</v>
+        <v>130010432</v>
       </c>
       <c r="B70" t="n">
         <v>79180</v>
@@ -7705,10 +7715,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>433482</v>
+        <v>432782</v>
       </c>
       <c r="R70" t="n">
-        <v>6765315</v>
+        <v>6765113</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7738,19 +7748,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>13:59</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7765,12 +7765,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8195,45 +8195,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130000798</v>
+        <v>130009990</v>
       </c>
       <c r="B75" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>432873</v>
+        <v>433472</v>
       </c>
       <c r="R75" t="n">
-        <v>6764999</v>
+        <v>6765327</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8290,12 +8290,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8506,45 +8506,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130009990</v>
+        <v>130000798</v>
       </c>
       <c r="B78" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>433472</v>
+        <v>432873</v>
       </c>
       <c r="R78" t="n">
-        <v>6765327</v>
+        <v>6764999</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8601,12 +8601,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 56940-2025 artfynd.xlsx
+++ b/artfynd/A 56940-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY83"/>
+  <dimension ref="A1:AY84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9137,6 +9137,109 @@
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>129998720</v>
+      </c>
+      <c r="B84" t="n">
+        <v>5178</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljoten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>432741</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6764935</v>
+      </c>
+      <c r="S84" t="n">
+        <v>1</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56940-2025 artfynd.xlsx
+++ b/artfynd/A 56940-2025 artfynd.xlsx
@@ -9142,7 +9142,7 @@
         <v>129998720</v>
       </c>
       <c r="B84" t="n">
-        <v>5178</v>
+        <v>5179</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 56940-2025 artfynd.xlsx
+++ b/artfynd/A 56940-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY84"/>
+  <dimension ref="A1:AY87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129998685</v>
+        <v>129998689</v>
       </c>
       <c r="B2" t="n">
-        <v>79770</v>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>433147</v>
+        <v>433431</v>
       </c>
       <c r="R2" t="n">
-        <v>6765200</v>
+        <v>6765309</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -754,6 +754,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,10 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129998684</v>
+        <v>130009980</v>
       </c>
       <c r="B3" t="n">
-        <v>79770</v>
+        <v>90932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +784,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljoten, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>433295</v>
+        <v>433320</v>
       </c>
       <c r="R3" t="n">
-        <v>6765131</v>
+        <v>6765160</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -840,77 +841,88 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129998703</v>
+        <v>130010424</v>
       </c>
       <c r="B4" t="n">
-        <v>8451</v>
+        <v>90932</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljoten, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432909</v>
+        <v>433000</v>
       </c>
       <c r="R4" t="n">
-        <v>6765182</v>
+        <v>6765168</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,22 +966,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129998697</v>
+        <v>130010425</v>
       </c>
       <c r="B5" t="n">
-        <v>78938</v>
+        <v>90932</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,37 +989,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljoten, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>433506</v>
+        <v>432853</v>
       </c>
       <c r="R5" t="n">
-        <v>6765247</v>
+        <v>6765042</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,22 +1063,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129998708</v>
+        <v>130000808</v>
       </c>
       <c r="B6" t="n">
-        <v>78937</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,37 +1086,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljoten, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>433435</v>
+        <v>432783</v>
       </c>
       <c r="R6" t="n">
-        <v>6765311</v>
+        <v>6765102</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1131,39 +1147,50 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129998686</v>
+        <v>130010444</v>
       </c>
       <c r="B7" t="n">
-        <v>79770</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,37 +1198,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljoten, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>432885</v>
+        <v>433284</v>
       </c>
       <c r="R7" t="n">
-        <v>6765057</v>
+        <v>6765098</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,44 +1272,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129998706</v>
+        <v>129998690</v>
       </c>
       <c r="B8" t="n">
-        <v>8451</v>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>432738</v>
+        <v>433075</v>
       </c>
       <c r="R8" t="n">
-        <v>6764941</v>
+        <v>6765183</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1328,6 +1355,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 st. Inte samma träd som tickorna bredvid.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1354,10 +1386,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129998718</v>
+        <v>130009978</v>
       </c>
       <c r="B9" t="n">
-        <v>79181</v>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,37 +1397,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>230405</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljoten, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433287</v>
+        <v>433075</v>
       </c>
       <c r="R9" t="n">
-        <v>6765093</v>
+        <v>6765186</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1422,9 +1465,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1440,60 +1493,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129998704</v>
+        <v>130009979</v>
       </c>
       <c r="B10" t="n">
-        <v>8451</v>
+        <v>91930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljoten, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>432886</v>
+        <v>433285</v>
       </c>
       <c r="R10" t="n">
-        <v>6765067</v>
+        <v>6765090</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1520,9 +1573,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1537,60 +1600,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129998683</v>
+        <v>130000802</v>
       </c>
       <c r="B11" t="n">
-        <v>79770</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljoten, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433347</v>
+        <v>432785</v>
       </c>
       <c r="R11" t="n">
-        <v>6765088</v>
+        <v>6765104</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1617,9 +1680,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1634,39 +1707,39 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129998717</v>
+        <v>130000803</v>
       </c>
       <c r="B12" t="n">
-        <v>79181</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1677,17 +1750,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljoten, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433514</v>
+        <v>433436</v>
       </c>
       <c r="R12" t="n">
-        <v>6765225</v>
+        <v>6765320</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1714,78 +1787,87 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129998698</v>
+        <v>130000804</v>
       </c>
       <c r="B13" t="n">
-        <v>78938</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljoten, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432754</v>
+        <v>433364</v>
       </c>
       <c r="R13" t="n">
-        <v>6764932</v>
+        <v>6765087</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1812,9 +1894,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1829,60 +1921,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129998687</v>
+        <v>130000805</v>
       </c>
       <c r="B14" t="n">
-        <v>79770</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljoten, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432898</v>
+        <v>432810</v>
       </c>
       <c r="R14" t="n">
-        <v>6764900</v>
+        <v>6765134</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1909,9 +2001,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1926,39 +2028,39 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129998716</v>
+        <v>130000806</v>
       </c>
       <c r="B15" t="n">
-        <v>79181</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1969,17 +2071,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljoten, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433482</v>
+        <v>432829</v>
       </c>
       <c r="R15" t="n">
-        <v>6765312</v>
+        <v>6765145</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2006,78 +2108,87 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129998688</v>
+        <v>130000807</v>
       </c>
       <c r="B16" t="n">
-        <v>79770</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljoten, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>432786</v>
+        <v>432598</v>
       </c>
       <c r="R16" t="n">
-        <v>6764988</v>
+        <v>6764869</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2104,9 +2215,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2121,60 +2242,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129998690</v>
+        <v>130009988</v>
       </c>
       <c r="B17" t="n">
-        <v>91749</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljoten, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433075</v>
+        <v>433439</v>
       </c>
       <c r="R17" t="n">
-        <v>6765183</v>
+        <v>6765313</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2201,14 +2322,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>1 st. Inte samma träd som tickorna bredvid.</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2223,39 +2349,39 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129998719</v>
+        <v>130009989</v>
       </c>
       <c r="B18" t="n">
-        <v>79181</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2266,17 +2392,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljoten, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>432725</v>
+        <v>433473</v>
       </c>
       <c r="R18" t="n">
-        <v>6764934</v>
+        <v>6765313</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2303,78 +2429,87 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129998701</v>
+        <v>130009990</v>
       </c>
       <c r="B19" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljoten, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433145</v>
+        <v>433472</v>
       </c>
       <c r="R19" t="n">
-        <v>6765198</v>
+        <v>6765327</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2401,44 +2536,53 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130009997</v>
+        <v>130009991</v>
       </c>
       <c r="B20" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2466,10 +2610,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433474</v>
+        <v>433469</v>
       </c>
       <c r="R20" t="n">
-        <v>6765288</v>
+        <v>6765340</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2501,7 +2645,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2511,7 +2655,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2538,14 +2682,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130009995</v>
+        <v>130009992</v>
       </c>
       <c r="B21" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2573,10 +2717,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433498</v>
+        <v>433482</v>
       </c>
       <c r="R21" t="n">
-        <v>6765316</v>
+        <v>6765315</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2608,7 +2752,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2618,7 +2762,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2645,32 +2789,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130010431</v>
+        <v>130009993</v>
       </c>
       <c r="B22" t="n">
-        <v>78937</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2680,10 +2824,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>432755</v>
+        <v>433494</v>
       </c>
       <c r="R22" t="n">
-        <v>6764944</v>
+        <v>6765320</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2713,9 +2857,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2730,66 +2884,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130010428</v>
+        <v>130009994</v>
       </c>
       <c r="B23" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>432868</v>
+        <v>433500</v>
       </c>
       <c r="R23" t="n">
-        <v>6764991</v>
+        <v>6765331</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2819,62 +2964,71 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130010447</v>
+        <v>130009995</v>
       </c>
       <c r="B24" t="n">
-        <v>78187</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2884,10 +3038,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>432743</v>
+        <v>433498</v>
       </c>
       <c r="R24" t="n">
-        <v>6764890</v>
+        <v>6765316</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2917,9 +3071,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2934,26 +3098,26 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130000805</v>
+        <v>130009996</v>
       </c>
       <c r="B25" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2977,14 +3141,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>432810</v>
+        <v>433488</v>
       </c>
       <c r="R25" t="n">
-        <v>6765134</v>
+        <v>6765315</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3016,7 +3180,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3026,7 +3190,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3041,57 +3205,57 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130000797</v>
+        <v>130009997</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>432910</v>
+        <v>433474</v>
       </c>
       <c r="R26" t="n">
-        <v>6764964</v>
+        <v>6765288</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3123,7 +3287,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3133,7 +3297,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3148,26 +3312,26 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130010439</v>
+        <v>130009998</v>
       </c>
       <c r="B27" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3195,10 +3359,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>432941</v>
+        <v>433400</v>
       </c>
       <c r="R27" t="n">
-        <v>6764955</v>
+        <v>6765137</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3228,9 +3392,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3245,26 +3419,26 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130010002</v>
+        <v>130009999</v>
       </c>
       <c r="B28" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3292,10 +3466,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>432842</v>
+        <v>433404</v>
       </c>
       <c r="R28" t="n">
-        <v>6764945</v>
+        <v>6765152</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3327,7 +3501,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3337,7 +3511,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3364,14 +3538,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130000803</v>
+        <v>130010000</v>
       </c>
       <c r="B29" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3395,14 +3569,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>433436</v>
+        <v>432861</v>
       </c>
       <c r="R29" t="n">
-        <v>6765320</v>
+        <v>6764984</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3434,7 +3608,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3444,7 +3618,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3459,44 +3633,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130009976</v>
+        <v>130010001</v>
       </c>
       <c r="B30" t="n">
-        <v>79770</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3506,10 +3680,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>432806</v>
+        <v>432965</v>
       </c>
       <c r="R30" t="n">
-        <v>6764957</v>
+        <v>6764935</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3541,7 +3715,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3551,7 +3725,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3578,54 +3752,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130009984</v>
+        <v>130010002</v>
       </c>
       <c r="B31" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>432757</v>
+        <v>432842</v>
       </c>
       <c r="R31" t="n">
-        <v>6764953</v>
+        <v>6764945</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3657,7 +3822,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3667,7 +3832,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3676,7 +3841,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3695,32 +3859,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130010446</v>
+        <v>130010003</v>
       </c>
       <c r="B32" t="n">
-        <v>78187</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3730,10 +3894,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>432787</v>
+        <v>432841</v>
       </c>
       <c r="R32" t="n">
-        <v>6764952</v>
+        <v>6764949</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3763,9 +3927,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3780,26 +3954,26 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130009999</v>
+        <v>130010004</v>
       </c>
       <c r="B33" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -3827,10 +4001,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>433404</v>
+        <v>432836</v>
       </c>
       <c r="R33" t="n">
-        <v>6765152</v>
+        <v>6764947</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3862,7 +4036,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3872,7 +4046,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3899,14 +4073,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130010440</v>
+        <v>130010005</v>
       </c>
       <c r="B34" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -3934,10 +4108,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>432846</v>
+        <v>432732</v>
       </c>
       <c r="R34" t="n">
-        <v>6764945</v>
+        <v>6764932</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3967,9 +4141,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3984,44 +4168,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130009975</v>
+        <v>130010432</v>
       </c>
       <c r="B35" t="n">
-        <v>79770</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4031,10 +4215,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>432801</v>
+        <v>432782</v>
       </c>
       <c r="R35" t="n">
-        <v>6765083</v>
+        <v>6765113</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4064,19 +4248,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4091,57 +4265,57 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130000795</v>
+        <v>130010433</v>
       </c>
       <c r="B36" t="n">
-        <v>79770</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>432795</v>
+        <v>432809</v>
       </c>
       <c r="R36" t="n">
-        <v>6764980</v>
+        <v>6765129</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4171,19 +4345,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>10:47</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>10:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4198,44 +4362,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130009986</v>
+        <v>130010434</v>
       </c>
       <c r="B37" t="n">
-        <v>78937</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4245,10 +4409,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>432880</v>
+        <v>433459</v>
       </c>
       <c r="R37" t="n">
-        <v>6764902</v>
+        <v>6765287</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4278,19 +4442,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4305,44 +4459,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130009980</v>
+        <v>130010435</v>
       </c>
       <c r="B38" t="n">
-        <v>90760</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4352,10 +4506,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>433320</v>
+        <v>433498</v>
       </c>
       <c r="R38" t="n">
-        <v>6765160</v>
+        <v>6765212</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4385,72 +4539,61 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130010425</v>
+        <v>130010436</v>
       </c>
       <c r="B39" t="n">
-        <v>90760</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4460,10 +4603,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>432853</v>
+        <v>433362</v>
       </c>
       <c r="R39" t="n">
-        <v>6765042</v>
+        <v>6765100</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4522,54 +4665,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130009982</v>
+        <v>130010437</v>
       </c>
       <c r="B40" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>433497</v>
+        <v>433359</v>
       </c>
       <c r="R40" t="n">
-        <v>6765321</v>
+        <v>6765114</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4599,54 +4733,43 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130009998</v>
+        <v>130010438</v>
       </c>
       <c r="B41" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4674,10 +4797,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>433400</v>
+        <v>432834</v>
       </c>
       <c r="R41" t="n">
-        <v>6765137</v>
+        <v>6765072</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4707,19 +4830,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4734,26 +4847,26 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130010442</v>
+        <v>130010439</v>
       </c>
       <c r="B42" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -4781,10 +4894,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>432625</v>
+        <v>432941</v>
       </c>
       <c r="R42" t="n">
-        <v>6764870</v>
+        <v>6764955</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4843,32 +4956,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130010424</v>
+        <v>130010440</v>
       </c>
       <c r="B43" t="n">
-        <v>90760</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4878,10 +4991,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>433000</v>
+        <v>432846</v>
       </c>
       <c r="R43" t="n">
-        <v>6765168</v>
+        <v>6764945</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4940,54 +5053,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130010429</v>
+        <v>130010441</v>
       </c>
       <c r="B44" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>432898</v>
+        <v>432847</v>
       </c>
       <c r="R44" t="n">
-        <v>6764968</v>
+        <v>6764943</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5028,7 +5132,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5047,27 +5150,27 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130000800</v>
+        <v>130010442</v>
       </c>
       <c r="B45" t="n">
-        <v>79181</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5078,14 +5181,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>433464</v>
+        <v>432625</v>
       </c>
       <c r="R45" t="n">
-        <v>6765289</v>
+        <v>6764870</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5115,50 +5218,39 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130000806</v>
+        <v>129998708</v>
       </c>
       <c r="B46" t="n">
-        <v>79180</v>
+        <v>79084</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5166,37 +5258,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljoten, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>432829</v>
+        <v>433435</v>
       </c>
       <c r="R46" t="n">
-        <v>6765145</v>
+        <v>6765311</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5223,19 +5315,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5250,22 +5332,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130009993</v>
+        <v>130000799</v>
       </c>
       <c r="B47" t="n">
-        <v>79180</v>
+        <v>79084</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5273,34 +5355,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>433494</v>
+        <v>433372</v>
       </c>
       <c r="R47" t="n">
-        <v>6765320</v>
+        <v>6765077</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5332,7 +5414,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5342,7 +5424,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5357,44 +5439,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130010444</v>
+        <v>130009986</v>
       </c>
       <c r="B48" t="n">
-        <v>93010</v>
+        <v>79084</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5404,10 +5486,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>433284</v>
+        <v>432880</v>
       </c>
       <c r="R48" t="n">
-        <v>6765098</v>
+        <v>6764902</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5437,9 +5519,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5454,22 +5546,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130009994</v>
+        <v>130010431</v>
       </c>
       <c r="B49" t="n">
-        <v>79180</v>
+        <v>79084</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5477,21 +5569,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5501,10 +5593,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>433500</v>
+        <v>432755</v>
       </c>
       <c r="R49" t="n">
-        <v>6765331</v>
+        <v>6764944</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5534,19 +5626,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:57</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5561,22 +5643,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130010441</v>
+        <v>130010445</v>
       </c>
       <c r="B50" t="n">
-        <v>79180</v>
+        <v>78334</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5584,21 +5666,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5608,10 +5690,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>432847</v>
+        <v>433119</v>
       </c>
       <c r="R50" t="n">
-        <v>6764943</v>
+        <v>6765204</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5670,49 +5752,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130000808</v>
+        <v>130010446</v>
       </c>
       <c r="B51" t="n">
-        <v>93010</v>
+        <v>78334</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>432783</v>
+        <v>432787</v>
       </c>
       <c r="R51" t="n">
-        <v>6765102</v>
+        <v>6764952</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5742,50 +5820,39 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130010438</v>
+        <v>130010447</v>
       </c>
       <c r="B52" t="n">
-        <v>79180</v>
+        <v>78334</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5793,21 +5860,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5817,10 +5884,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>432834</v>
+        <v>432743</v>
       </c>
       <c r="R52" t="n">
-        <v>6765072</v>
+        <v>6764890</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5879,59 +5946,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130009978</v>
+        <v>129998720</v>
       </c>
       <c r="B53" t="n">
-        <v>91749</v>
+        <v>5181</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnsfljoten, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>433075</v>
+        <v>432741</v>
       </c>
       <c r="R53" t="n">
-        <v>6765186</v>
+        <v>6764935</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5958,19 +6019,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>14:39</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>14:39</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5986,22 +6037,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130009983</v>
+        <v>129998701</v>
       </c>
       <c r="B54" t="n">
-        <v>8451</v>
+        <v>8455</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6027,28 +6078,19 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnsfljoten, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>432870</v>
+        <v>433145</v>
       </c>
       <c r="R54" t="n">
-        <v>6764928</v>
+        <v>6765198</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6075,19 +6117,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6103,60 +6135,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130010437</v>
+        <v>129998703</v>
       </c>
       <c r="B55" t="n">
-        <v>79180</v>
+        <v>8455</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnsfljoten, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>433359</v>
+        <v>432909</v>
       </c>
       <c r="R55" t="n">
-        <v>6765114</v>
+        <v>6765182</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6200,60 +6232,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130000802</v>
+        <v>129998704</v>
       </c>
       <c r="B56" t="n">
-        <v>79180</v>
+        <v>8455</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljoten, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>432785</v>
+        <v>432886</v>
       </c>
       <c r="R56" t="n">
-        <v>6765104</v>
+        <v>6765067</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6280,19 +6312,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>14:54</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6307,22 +6329,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130010427</v>
+        <v>129998706</v>
       </c>
       <c r="B57" t="n">
-        <v>8451</v>
+        <v>8455</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6350,17 +6372,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnsfljoten, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>433049</v>
+        <v>432738</v>
       </c>
       <c r="R57" t="n">
-        <v>6765172</v>
+        <v>6764941</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6404,57 +6426,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130010423</v>
+        <v>130000796</v>
       </c>
       <c r="B58" t="n">
-        <v>79770</v>
+        <v>8455</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>432753</v>
+        <v>433217</v>
       </c>
       <c r="R58" t="n">
-        <v>6765037</v>
+        <v>6765206</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6484,9 +6506,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6501,22 +6533,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130009981</v>
+        <v>130000797</v>
       </c>
       <c r="B59" t="n">
-        <v>8451</v>
+        <v>8455</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6542,25 +6574,16 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>433429</v>
+        <v>432910</v>
       </c>
       <c r="R59" t="n">
-        <v>6765324</v>
+        <v>6764964</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6592,7 +6615,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6602,7 +6625,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6611,64 +6634,63 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130010436</v>
+        <v>130000798</v>
       </c>
       <c r="B60" t="n">
-        <v>79180</v>
+        <v>8455</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>433362</v>
+        <v>432873</v>
       </c>
       <c r="R60" t="n">
-        <v>6765100</v>
+        <v>6764999</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6698,9 +6720,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6715,57 +6747,66 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130009989</v>
+        <v>130009981</v>
       </c>
       <c r="B61" t="n">
-        <v>79180</v>
+        <v>8455</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>433473</v>
+        <v>433429</v>
       </c>
       <c r="R61" t="n">
-        <v>6765313</v>
+        <v>6765324</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6797,7 +6838,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6807,7 +6848,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6816,6 +6857,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6834,45 +6876,54 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130009991</v>
+        <v>130009982</v>
       </c>
       <c r="B62" t="n">
-        <v>79180</v>
+        <v>8455</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>433469</v>
+        <v>433497</v>
       </c>
       <c r="R62" t="n">
-        <v>6765340</v>
+        <v>6765321</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6904,7 +6955,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -6914,7 +6965,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6923,6 +6974,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6941,45 +6993,54 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130010000</v>
+        <v>130009983</v>
       </c>
       <c r="B63" t="n">
-        <v>79180</v>
+        <v>8455</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>432861</v>
+        <v>432870</v>
       </c>
       <c r="R63" t="n">
-        <v>6764984</v>
+        <v>6764928</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7011,7 +7072,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7021,7 +7082,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7030,6 +7091,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7048,45 +7110,54 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130010434</v>
+        <v>130009984</v>
       </c>
       <c r="B64" t="n">
-        <v>79180</v>
+        <v>8455</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>433459</v>
+        <v>432757</v>
       </c>
       <c r="R64" t="n">
-        <v>6765287</v>
+        <v>6764953</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7116,74 +7187,94 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130010004</v>
+        <v>130009987</v>
       </c>
       <c r="B65" t="n">
-        <v>79180</v>
+        <v>8455</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432836</v>
+        <v>433174</v>
       </c>
       <c r="R65" t="n">
-        <v>6764947</v>
+        <v>6765214</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7215,7 +7306,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7225,7 +7316,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7234,6 +7325,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7252,45 +7344,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130009979</v>
+        <v>130010426</v>
       </c>
       <c r="B66" t="n">
-        <v>91749</v>
+        <v>8455</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>433285</v>
+        <v>433443</v>
       </c>
       <c r="R66" t="n">
-        <v>6765090</v>
+        <v>6765297</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7320,49 +7421,40 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130010426</v>
+        <v>130010427</v>
       </c>
       <c r="B67" t="n">
-        <v>8451</v>
+        <v>8455</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7388,25 +7480,16 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>433443</v>
+        <v>433049</v>
       </c>
       <c r="R67" t="n">
-        <v>6765297</v>
+        <v>6765172</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7447,7 +7530,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7466,45 +7548,54 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130009992</v>
+        <v>130010428</v>
       </c>
       <c r="B68" t="n">
-        <v>79180</v>
+        <v>8455</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>433482</v>
+        <v>432868</v>
       </c>
       <c r="R68" t="n">
-        <v>6765315</v>
+        <v>6764991</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7534,84 +7625,84 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130009996</v>
+        <v>130010429</v>
       </c>
       <c r="B69" t="n">
-        <v>79180</v>
+        <v>8455</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>433488</v>
+        <v>432898</v>
       </c>
       <c r="R69" t="n">
-        <v>6765315</v>
+        <v>6764968</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7641,84 +7732,84 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130010432</v>
+        <v>130010430</v>
       </c>
       <c r="B70" t="n">
-        <v>79180</v>
+        <v>8455</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>432782</v>
+        <v>432802</v>
       </c>
       <c r="R70" t="n">
-        <v>6765113</v>
+        <v>6764963</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7759,6 +7850,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7777,10 +7869,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130010001</v>
+        <v>129998697</v>
       </c>
       <c r="B71" t="n">
-        <v>79180</v>
+        <v>79085</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7788,37 +7880,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnsfljoten, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>432965</v>
+        <v>433506</v>
       </c>
       <c r="R71" t="n">
-        <v>6764935</v>
+        <v>6765247</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7845,19 +7937,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>11:24</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7872,60 +7954,60 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130000796</v>
+        <v>129998698</v>
       </c>
       <c r="B72" t="n">
-        <v>8451</v>
+        <v>79085</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljoten, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>433217</v>
+        <v>432754</v>
       </c>
       <c r="R72" t="n">
-        <v>6765206</v>
+        <v>6764932</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7952,19 +8034,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>12:40</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7979,22 +8051,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130010433</v>
+        <v>129998683</v>
       </c>
       <c r="B73" t="n">
-        <v>79180</v>
+        <v>79917</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8002,37 +8074,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnsfljoten, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432809</v>
+        <v>433347</v>
       </c>
       <c r="R73" t="n">
-        <v>6765129</v>
+        <v>6765088</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8076,22 +8148,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130010005</v>
+        <v>129998684</v>
       </c>
       <c r="B74" t="n">
-        <v>79180</v>
+        <v>79917</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8099,37 +8171,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnsfljoten, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>432732</v>
+        <v>433295</v>
       </c>
       <c r="R74" t="n">
-        <v>6764932</v>
+        <v>6765131</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8156,19 +8228,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>10:35</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8183,22 +8245,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130009990</v>
+        <v>129998685</v>
       </c>
       <c r="B75" t="n">
-        <v>79180</v>
+        <v>79917</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8206,37 +8268,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnsfljoten, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>433472</v>
+        <v>433147</v>
       </c>
       <c r="R75" t="n">
-        <v>6765327</v>
+        <v>6765200</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8263,19 +8325,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>14:00</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8290,22 +8342,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130010435</v>
+        <v>129998686</v>
       </c>
       <c r="B76" t="n">
-        <v>79180</v>
+        <v>79917</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8313,37 +8365,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnsfljoten, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>433498</v>
+        <v>432885</v>
       </c>
       <c r="R76" t="n">
-        <v>6765212</v>
+        <v>6765057</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8387,22 +8439,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130009988</v>
+        <v>129998687</v>
       </c>
       <c r="B77" t="n">
-        <v>79180</v>
+        <v>79917</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8410,37 +8462,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnsfljoten, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>433439</v>
+        <v>432898</v>
       </c>
       <c r="R77" t="n">
-        <v>6765313</v>
+        <v>6764900</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8467,19 +8519,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>14:09</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8494,60 +8536,60 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130000798</v>
+        <v>129998688</v>
       </c>
       <c r="B78" t="n">
-        <v>8451</v>
+        <v>79917</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Fisktjärnfjot, Dlr</t>
+          <t>Fisktjärnsfljoten, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>432873</v>
+        <v>432786</v>
       </c>
       <c r="R78" t="n">
-        <v>6764999</v>
+        <v>6764988</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8574,19 +8616,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8601,22 +8633,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130010003</v>
+        <v>130000795</v>
       </c>
       <c r="B79" t="n">
-        <v>79180</v>
+        <v>79917</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8624,34 +8656,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Fisktjärnsfljot, Dlr</t>
+          <t>Fisktjärnfjot, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>432841</v>
+        <v>432795</v>
       </c>
       <c r="R79" t="n">
-        <v>6764949</v>
+        <v>6764980</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8683,7 +8715,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8693,7 +8725,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8708,22 +8740,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130010445</v>
+        <v>130009975</v>
       </c>
       <c r="B80" t="n">
-        <v>78187</v>
+        <v>79917</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8731,21 +8763,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8755,10 +8787,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>433119</v>
+        <v>432801</v>
       </c>
       <c r="R80" t="n">
-        <v>6765204</v>
+        <v>6765083</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8788,9 +8820,19 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8805,66 +8847,57 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130010430</v>
+        <v>130009976</v>
       </c>
       <c r="B81" t="n">
-        <v>8451</v>
+        <v>79917</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>432802</v>
+        <v>432806</v>
       </c>
       <c r="R81" t="n">
-        <v>6764963</v>
+        <v>6764957</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8894,84 +8927,84 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130009987</v>
+        <v>130010423</v>
       </c>
       <c r="B82" t="n">
-        <v>8451</v>
+        <v>79917</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Fisktjärnsfljot, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>433174</v>
+        <v>432753</v>
       </c>
       <c r="R82" t="n">
-        <v>6765214</v>
+        <v>6765037</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9001,50 +9034,39 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129998689</v>
+        <v>129998716</v>
       </c>
       <c r="B83" t="n">
-        <v>92001</v>
+        <v>79328</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9052,21 +9074,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>65</v>
+        <v>230405</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9076,10 +9098,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>433431</v>
+        <v>433482</v>
       </c>
       <c r="R83" t="n">
-        <v>6765309</v>
+        <v>6765312</v>
       </c>
       <c r="S83" t="n">
         <v>1</v>
@@ -9139,50 +9161,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129998720</v>
+        <v>129998717</v>
       </c>
       <c r="B84" t="n">
-        <v>5179</v>
+        <v>79328</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100526</v>
+        <v>230405</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Fisktjärnsfljoten, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>432741</v>
+        <v>433514</v>
       </c>
       <c r="R84" t="n">
-        <v>6764935</v>
+        <v>6765225</v>
       </c>
       <c r="S84" t="n">
         <v>1</v>
@@ -9239,6 +9256,310 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>129998718</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljoten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>433287</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6765093</v>
+      </c>
+      <c r="S85" t="n">
+        <v>1</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>129998719</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Fisktjärnsfljoten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>432725</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6764934</v>
+      </c>
+      <c r="S86" t="n">
+        <v>1</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>130000800</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Fisktjärnfjot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>433464</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6765289</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56940-2025 artfynd.xlsx
+++ b/artfynd/A 56940-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY87"/>
+  <dimension ref="A1:AZ87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129998689</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130009980</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010424</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010425</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130000808</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1281,6 +1311,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010444</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1383,6 +1418,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129998690</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1502,6 +1542,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130009978</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1609,6 +1654,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130009979</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1716,6 +1766,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130000802</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1823,6 +1878,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130000803</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1930,6 +1990,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130000804</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2037,6 +2102,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130000805</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2144,6 +2214,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130000806</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2251,6 +2326,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130000807</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2358,6 +2438,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130009988</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2465,6 +2550,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130009989</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2572,6 +2662,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130009990</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2679,6 +2774,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130009991</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2786,6 +2886,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130009992</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2893,6 +2998,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130009993</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3000,6 +3110,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130009994</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3107,6 +3222,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130009995</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3214,6 +3334,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130009996</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3321,6 +3446,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130009997</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3428,6 +3558,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130009998</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3535,6 +3670,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130009999</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3642,6 +3782,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010000</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3749,6 +3894,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010001</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3856,6 +4006,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010002</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3963,6 +4118,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010003</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4070,6 +4230,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010004</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4177,6 +4342,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010005</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4274,6 +4444,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010432</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4371,6 +4546,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010433</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4468,6 +4648,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010434</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4565,6 +4750,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010435</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4662,6 +4852,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010436</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4759,6 +4954,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010437</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4856,6 +5056,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010438</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4953,6 +5158,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010439</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5050,6 +5260,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010440</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5147,6 +5362,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010441</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5244,6 +5464,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010442</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5341,6 +5566,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129998708</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5448,6 +5678,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130000799</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5555,6 +5790,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130009986</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5652,6 +5892,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010431</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5749,6 +5994,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010445</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5846,6 +6096,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010446</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5943,6 +6198,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010447</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6046,6 +6306,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129998720</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6144,6 +6409,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129998701</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6241,6 +6511,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129998703</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6338,6 +6613,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129998704</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6435,6 +6715,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129998706</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6542,6 +6827,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130000796</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6649,6 +6939,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130000797</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6756,6 +7051,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130000798</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6873,6 +7173,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130009981</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6990,6 +7295,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130009982</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7107,6 +7417,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130009983</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7224,6 +7539,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130009984</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7341,6 +7661,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130009987</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7448,6 +7773,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010426</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7545,6 +7875,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010427</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7652,6 +7987,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010428</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7759,6 +8099,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010429</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7866,6 +8211,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010430</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7963,6 +8313,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129998697</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8060,6 +8415,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129998698</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8157,6 +8517,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129998683</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8254,6 +8619,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129998684</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8351,6 +8721,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129998685</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8448,6 +8823,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129998686</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8545,6 +8925,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129998687</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8642,6 +9027,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129998688</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8749,6 +9139,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130000795</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8856,6 +9251,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130009975</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8963,6 +9363,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130009976</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9060,6 +9465,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130010423</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9158,6 +9568,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129998716</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9256,6 +9671,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129998717</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9354,6 +9774,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129998718</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9452,6 +9877,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129998719</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9560,8 +9990,101 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130000800</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>